--- a/CATI/Analysis/QC/output/L2PHL_Questionnaire_Cross_Round_Report.xlsx
+++ b/CATI/Analysis/QC/output/L2PHL_Questionnaire_Cross_Round_Report.xlsx
@@ -1197,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2677,8 +2677,40 @@
       <c r="Q29" s="57" t="n"/>
       <c r="R29" s="58" t="n"/>
     </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B30" s="79" t="inlineStr"/>
+      <c r="C30" s="57" t="n"/>
+      <c r="D30" s="57" t="n"/>
+      <c r="E30" s="57" t="n"/>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="57" t="n"/>
+      <c r="I30" s="57" t="n"/>
+      <c r="J30" s="58" t="n"/>
+      <c r="K30" s="79" t="inlineStr">
+        <is>
+          <t>ic4_index_str</t>
+        </is>
+      </c>
+      <c r="L30" s="57" t="n"/>
+      <c r="M30" s="57" t="n"/>
+      <c r="N30" s="58" t="n"/>
+      <c r="O30" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P30" s="57" t="n"/>
+      <c r="Q30" s="57" t="n"/>
+      <c r="R30" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="B23:J23"/>
@@ -2689,12 +2721,15 @@
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="K25:N25"/>
     <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K30:N30"/>
     <mergeCell ref="O28:R28"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="A20:R20"/>
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O30:R30"/>
     <mergeCell ref="K29:N29"/>
     <mergeCell ref="B26:J26"/>
     <mergeCell ref="O29:R29"/>
@@ -2715,1502 +2750,6 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="35" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="35" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>M06 – Finance  |  Cross-Round Variable Tracker  (R1–R5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="55" t="inlineStr"/>
-      <c r="B2" s="55" t="inlineStr"/>
-      <c r="C2" s="55" t="inlineStr"/>
-      <c r="D2" s="56" t="inlineStr">
-        <is>
-          <t>R1
-Nov 2025</t>
-        </is>
-      </c>
-      <c r="E2" s="57" t="n"/>
-      <c r="F2" s="57" t="n"/>
-      <c r="G2" s="57" t="n"/>
-      <c r="H2" s="58" t="n"/>
-      <c r="I2" s="55" t="inlineStr"/>
-      <c r="J2" s="55" t="inlineStr"/>
-      <c r="K2" s="55" t="inlineStr"/>
-      <c r="L2" s="55" t="inlineStr"/>
-      <c r="M2" s="55" t="inlineStr"/>
-      <c r="N2" s="55" t="inlineStr"/>
-      <c r="O2" s="55" t="inlineStr"/>
-      <c r="P2" s="55" t="inlineStr"/>
-      <c r="Q2" s="55" t="inlineStr"/>
-      <c r="R2" s="55" t="inlineStr"/>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B3" s="59" t="inlineStr">
-        <is>
-          <t>Question Title</t>
-        </is>
-      </c>
-      <c r="C3" s="59" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D3" s="59" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E3" s="59" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F3" s="59" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="G3" s="59" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="H3" s="59" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="I3" s="59" t="inlineStr">
-        <is>
-          <t>Question Text (English)</t>
-        </is>
-      </c>
-      <c r="J3" s="59" t="inlineStr">
-        <is>
-          <t>Question Type</t>
-        </is>
-      </c>
-      <c r="K3" s="59" t="inlineStr">
-        <is>
-          <t># Codes R1</t>
-        </is>
-      </c>
-      <c r="L3" s="59" t="inlineStr">
-        <is>
-          <t># Codes R5</t>
-        </is>
-      </c>
-      <c r="M3" s="59" t="inlineStr">
-        <is>
-          <t>Title / Wording Change</t>
-        </is>
-      </c>
-      <c r="N3" s="59" t="inlineStr">
-        <is>
-          <t>Skip Logic Change</t>
-        </is>
-      </c>
-      <c r="O3" s="59" t="inlineStr">
-        <is>
-          <t>Skip Logic (R1)</t>
-        </is>
-      </c>
-      <c r="P3" s="59" t="inlineStr">
-        <is>
-          <t>Skip Logic (R5)</t>
-        </is>
-      </c>
-      <c r="Q3" s="59" t="inlineStr">
-        <is>
-          <t>Data Check Notes (R5)</t>
-        </is>
-      </c>
-      <c r="R3" s="59" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
-        <is>
-          <t>F17</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF HAVING A FORMAL BANK ACCOUNT</t>
-        </is>
-      </c>
-      <c r="C4" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D4" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>Do you or anyone in your household own a formal bank account?</t>
-        </is>
-      </c>
-      <c r="J4" s="37" t="inlineStr"/>
-      <c r="K4" s="33" t="inlineStr"/>
-      <c r="L4" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="37" t="inlineStr"/>
-      <c r="N4" s="72" t="inlineStr">
-        <is>
-          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O4" s="37" t="inlineStr"/>
-      <c r="P4" s="37" t="inlineStr">
-        <is>
-          <t>Code 1: Go to F1; Code 2: Go to F18</t>
-        </is>
-      </c>
-      <c r="Q4" s="37" t="inlineStr"/>
-      <c r="R4" s="37" t="inlineStr">
-        <is>
-          <t>Added in R5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="66" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B5" s="67" t="inlineStr">
-        <is>
-          <t>WHETHER A HH MEMBER DEPOSITED MONEY IN A FORMAL BANK ACCOUNT IN THE P30D</t>
-        </is>
-      </c>
-      <c r="C5" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I5" s="68" t="inlineStr">
-        <is>
-          <t>Has anyone in your household received or deposited money into a formal bank account over the PAST MONTH?</t>
-        </is>
-      </c>
-      <c r="J5" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K5" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="68" t="inlineStr"/>
-      <c r="N5" s="68" t="inlineStr"/>
-      <c r="O5" s="68" t="inlineStr"/>
-      <c r="P5" s="68" t="inlineStr"/>
-      <c r="Q5" s="70" t="inlineStr">
-        <is>
-          <t>Ensure every household has a response (Yes/No).</t>
-        </is>
-      </c>
-      <c r="R5" s="68" t="inlineStr">
-        <is>
-          <t>Change samabahayan to sambahayan
-Revised Past 30 Days to Past Month to align with phrasing of Income module questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="73" t="inlineStr">
-        <is>
-          <t>F18</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF HAVING A MOBILE MONEY ACCOUNT</t>
-        </is>
-      </c>
-      <c r="C6" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D6" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>Do you or anyone in your household own a mobile money account such as Gcash, Maya, etc?</t>
-        </is>
-      </c>
-      <c r="J6" s="37" t="inlineStr"/>
-      <c r="K6" s="33" t="inlineStr"/>
-      <c r="L6" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="37" t="inlineStr"/>
-      <c r="N6" s="72" t="inlineStr">
-        <is>
-          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O6" s="37" t="inlineStr"/>
-      <c r="P6" s="37" t="inlineStr">
-        <is>
-          <t>Code 1: Go to F2; Code 2: Go to F3</t>
-        </is>
-      </c>
-      <c r="Q6" s="37" t="inlineStr"/>
-      <c r="R6" s="37" t="inlineStr">
-        <is>
-          <t>Added in R5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="66" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="inlineStr">
-        <is>
-          <t>WHETHER A HH MEMBER RECEIVED/DEPOSITED MONEY INTO MOBILE BANKING SERVICE IN THE P30D</t>
-        </is>
-      </c>
-      <c r="C7" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="68" t="inlineStr">
-        <is>
-          <t>Has anyone in your household received or deposited money into Mobile Money service or an electronic wallet service over the PAST MONTH?</t>
-        </is>
-      </c>
-      <c r="J7" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K7" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" s="68" t="inlineStr"/>
-      <c r="N7" s="68" t="inlineStr"/>
-      <c r="O7" s="68" t="inlineStr"/>
-      <c r="P7" s="68" t="inlineStr"/>
-      <c r="Q7" s="68" t="inlineStr"/>
-      <c r="R7" s="68" t="inlineStr"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF SAVING SOME MONEY FOR THE FUTURE IN THE P30D</t>
-        </is>
-      </c>
-      <c r="C8" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="64" t="inlineStr">
-        <is>
-          <t>Given your financial commitments, were you able to save some money for the future over the PAST MONTH?</t>
-        </is>
-      </c>
-      <c r="J8" s="64" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K8" s="65" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="65" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="64" t="inlineStr"/>
-      <c r="N8" s="64" t="inlineStr"/>
-      <c r="O8" s="64" t="inlineStr"/>
-      <c r="P8" s="64" t="inlineStr"/>
-      <c r="Q8" s="64" t="inlineStr"/>
-      <c r="R8" s="64" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="B9" s="67" t="inlineStr">
-        <is>
-          <t>WHETHER HH CAN PAY AN EMERGENCY EXPENSE USING CASH, SAVINGS, OR OTHER RESOURCES ON HAND</t>
-        </is>
-      </c>
-      <c r="C9" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="68" t="inlineStr">
-        <is>
-          <t>Could your household currently pay an emergency expense of PhP50,000, using cash, savings, or other resources you have on-hand?</t>
-        </is>
-      </c>
-      <c r="J9" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K9" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" s="68" t="inlineStr"/>
-      <c r="N9" s="68" t="inlineStr"/>
-      <c r="O9" s="68" t="inlineStr"/>
-      <c r="P9" s="68" t="inlineStr"/>
-      <c r="Q9" s="68" t="inlineStr"/>
-      <c r="R9" s="68" t="inlineStr">
-        <is>
-          <t>Revised amount from 300k to 50k</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
-        <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF APPLYING FOR CREDIT/LOAN IN THE P30D</t>
-        </is>
-      </c>
-      <c r="C10" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="27" t="inlineStr">
-        <is>
-          <t>Did you or any other member of your household apply or try to take on credit or a loan in the PAST MONTH?</t>
-        </is>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" s="27" t="inlineStr"/>
-      <c r="N10" s="72" t="inlineStr">
-        <is>
-          <t>Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O10" s="27" t="inlineStr">
-        <is>
-          <t>Code 1: Go to F8; Code 2: Go to F13; Code 98: Go to F13, Use "-"; Code 99: Go to F13</t>
-        </is>
-      </c>
-      <c r="P10" s="27" t="inlineStr">
-        <is>
-          <t>Code 1: Go to F8; Code 2: Go to F13; Code 98: Go to F13, Use "-"; Code 99: Go to F13</t>
-        </is>
-      </c>
-      <c r="Q10" s="27" t="inlineStr"/>
-      <c r="R10" s="27" t="inlineStr"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="66" t="inlineStr">
-        <is>
-          <t>F8</t>
-        </is>
-      </c>
-      <c r="B11" s="67" t="inlineStr">
-        <is>
-          <t>PURPOSE OF LOAN</t>
-        </is>
-      </c>
-      <c r="C11" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="68" t="inlineStr">
-        <is>
-          <t>For what purpose?</t>
-        </is>
-      </c>
-      <c r="J11" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K11" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" s="68" t="inlineStr"/>
-      <c r="N11" s="68" t="inlineStr"/>
-      <c r="O11" s="68" t="inlineStr"/>
-      <c r="P11" s="68" t="inlineStr"/>
-      <c r="Q11" s="70" t="inlineStr">
-        <is>
-          <t>Recode code 96</t>
-        </is>
-      </c>
-      <c r="R11" s="68" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="B12" s="61" t="inlineStr">
-        <is>
-          <t>WHERE APPLIED FOR LOAN</t>
-        </is>
-      </c>
-      <c r="C12" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I12" s="64" t="inlineStr">
-        <is>
-          <t>To which institution or person did you or any other member of your household apply? (in the case of multiple, answer for the largest loan or credit)</t>
-        </is>
-      </c>
-      <c r="J12" s="64" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K12" s="65" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="65" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="64" t="inlineStr"/>
-      <c r="N12" s="64" t="inlineStr"/>
-      <c r="O12" s="64" t="inlineStr"/>
-      <c r="P12" s="64" t="inlineStr"/>
-      <c r="Q12" s="70" t="inlineStr">
-        <is>
-          <t>Recode code 96</t>
-        </is>
-      </c>
-      <c r="R12" s="64" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="66" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B13" s="67" t="inlineStr">
-        <is>
-          <t>WHETHER LOAN WAS APPROVED</t>
-        </is>
-      </c>
-      <c r="C13" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I13" s="68" t="inlineStr">
-        <is>
-          <t>Was the loan approved?</t>
-        </is>
-      </c>
-      <c r="J13" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K13" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="68" t="inlineStr"/>
-      <c r="N13" s="68" t="inlineStr"/>
-      <c r="O13" s="68" t="inlineStr"/>
-      <c r="P13" s="68" t="inlineStr"/>
-      <c r="Q13" s="68" t="inlineStr"/>
-      <c r="R13" s="68" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
-        <is>
-          <t>F14</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF USING MOBILE PHONE TO SEND MONEY</t>
-        </is>
-      </c>
-      <c r="C14" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I14" s="64" t="inlineStr">
-        <is>
-          <t>In the PAST MONTH, have you used a mobile phone to send money to someone else?</t>
-        </is>
-      </c>
-      <c r="J14" s="64" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K14" s="65" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="65" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="64" t="inlineStr"/>
-      <c r="N14" s="64" t="inlineStr"/>
-      <c r="O14" s="64" t="inlineStr"/>
-      <c r="P14" s="64" t="inlineStr"/>
-      <c r="Q14" s="64" t="inlineStr"/>
-      <c r="R14" s="64" t="inlineStr">
-        <is>
-          <t>Source: WB Findex 2021
-In the PAST 12 MONTHS, have you used a mobile phone to make payments, buy things, or to send or receive money?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>F15</t>
-        </is>
-      </c>
-      <c r="B15" s="67" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF USING MOBILE PHONE TO BUY ONLINE</t>
-        </is>
-      </c>
-      <c r="C15" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I15" s="68" t="inlineStr">
-        <is>
-          <t>In the PAST MONTH, have you used a mobile phone to buy something online?</t>
-        </is>
-      </c>
-      <c r="J15" s="68" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K15" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="68" t="inlineStr"/>
-      <c r="N15" s="68" t="inlineStr"/>
-      <c r="O15" s="68" t="inlineStr"/>
-      <c r="P15" s="68" t="inlineStr"/>
-      <c r="Q15" s="68" t="inlineStr"/>
-      <c r="R15" s="68" t="inlineStr"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
-        <is>
-          <t>F16</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF EXPERIENCING EITHER ATTEMPTED/SUCCESSFUL FRAUD/THEFT/OTHER FINANCIAL LOSS</t>
-        </is>
-      </c>
-      <c r="C16" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I16" s="64" t="inlineStr">
-        <is>
-          <t>In the PAST MONTH, have you or any household member experienced either attempted or successful fraud, theft, or other financial loss?</t>
-        </is>
-      </c>
-      <c r="J16" s="64" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K16" s="65" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="65" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="64" t="inlineStr"/>
-      <c r="N16" s="64" t="inlineStr"/>
-      <c r="O16" s="64" t="inlineStr"/>
-      <c r="P16" s="64" t="inlineStr"/>
-      <c r="Q16" s="64" t="inlineStr"/>
-      <c r="R16" s="64" t="inlineStr">
-        <is>
-          <t>Source: L2Indonesia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="66" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="B17" s="67" t="inlineStr"/>
-      <c r="C17" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I17" s="68" t="inlineStr"/>
-      <c r="J17" s="68" t="inlineStr"/>
-      <c r="K17" s="69" t="inlineStr"/>
-      <c r="L17" s="69" t="inlineStr"/>
-      <c r="M17" s="68" t="inlineStr"/>
-      <c r="N17" s="68" t="inlineStr"/>
-      <c r="O17" s="68" t="inlineStr"/>
-      <c r="P17" s="68" t="inlineStr"/>
-      <c r="Q17" s="68" t="inlineStr"/>
-      <c r="R17" s="68" t="inlineStr"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
-        <is>
-          <t>F13</t>
-        </is>
-      </c>
-      <c r="B18" s="61" t="inlineStr">
-        <is>
-          <t>WAYS OF RECEIVING REMITTANCES</t>
-        </is>
-      </c>
-      <c r="C18" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I18" s="64" t="inlineStr">
-        <is>
-          <t>In the PAST MONTH, have you or any member of your household RECEIVED remittances from family members or relatives who work in other city or other country in the following ways?</t>
-        </is>
-      </c>
-      <c r="J18" s="64" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K18" s="65" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" s="65" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" s="64" t="inlineStr"/>
-      <c r="N18" s="64" t="inlineStr"/>
-      <c r="O18" s="64" t="inlineStr"/>
-      <c r="P18" s="64" t="inlineStr"/>
-      <c r="Q18" s="64" t="inlineStr"/>
-      <c r="R18" s="64" t="inlineStr">
-        <is>
-          <t>Source: WB Findex 2021
-In the PAST 12 MONTHS, have you, personally, RECEIVED money from a relative or friend living in a different city or area inside (response in SA) in any of the following ways?</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="76" t="inlineStr">
-        <is>
-          <t>DO-FILE VARIABLE DETAILS (destring/generate operations per round)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="77" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-      <c r="B21" s="77" t="inlineStr">
-        <is>
-          <t>Variables processed (destring/tostring)</t>
-        </is>
-      </c>
-      <c r="C21" s="57" t="n"/>
-      <c r="D21" s="57" t="n"/>
-      <c r="E21" s="57" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="57" t="n"/>
-      <c r="H21" s="57" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="58" t="n"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="78" t="inlineStr">
-        <is>
-          <t>R1 (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="B22" s="79" t="inlineStr">
-        <is>
-          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="57" t="n"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="58" t="n"/>
-      <c r="K22" s="79" t="inlineStr">
-        <is>
-          <t>f8_18, f8_24, f8_25</t>
-        </is>
-      </c>
-      <c r="L22" s="57" t="n"/>
-      <c r="M22" s="57" t="n"/>
-      <c r="N22" s="58" t="n"/>
-      <c r="O22" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P22" s="57" t="n"/>
-      <c r="Q22" s="57" t="n"/>
-      <c r="R22" s="58" t="n"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="80" t="inlineStr">
-        <is>
-          <t>R2 (Dec 2025)</t>
-        </is>
-      </c>
-      <c r="B23" s="81" t="inlineStr">
-        <is>
-          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="n"/>
-      <c r="D23" s="57" t="n"/>
-      <c r="E23" s="57" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="57" t="n"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="58" t="n"/>
-      <c r="K23" s="81" t="inlineStr"/>
-      <c r="L23" s="57" t="n"/>
-      <c r="M23" s="57" t="n"/>
-      <c r="N23" s="58" t="n"/>
-      <c r="O23" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P23" s="57" t="n"/>
-      <c r="Q23" s="57" t="n"/>
-      <c r="R23" s="58" t="n"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="78" t="inlineStr">
-        <is>
-          <t>R3 (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="B24" s="79" t="inlineStr">
-        <is>
-          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="57" t="n"/>
-      <c r="H24" s="57" t="n"/>
-      <c r="I24" s="57" t="n"/>
-      <c r="J24" s="58" t="n"/>
-      <c r="K24" s="79" t="inlineStr"/>
-      <c r="L24" s="57" t="n"/>
-      <c r="M24" s="57" t="n"/>
-      <c r="N24" s="58" t="n"/>
-      <c r="O24" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P24" s="57" t="n"/>
-      <c r="Q24" s="57" t="n"/>
-      <c r="R24" s="58" t="n"/>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="80" t="inlineStr">
-        <is>
-          <t>R4 (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="B25" s="81" t="inlineStr">
-        <is>
-          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C25" s="57" t="n"/>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="57" t="n"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="58" t="n"/>
-      <c r="K25" s="81" t="inlineStr"/>
-      <c r="L25" s="57" t="n"/>
-      <c r="M25" s="57" t="n"/>
-      <c r="N25" s="58" t="n"/>
-      <c r="O25" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P25" s="57" t="n"/>
-      <c r="Q25" s="57" t="n"/>
-      <c r="R25" s="58" t="n"/>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="78" t="inlineStr">
-        <is>
-          <t>R5 (Mar 2026)</t>
-        </is>
-      </c>
-      <c r="B26" s="79" t="inlineStr">
-        <is>
-          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C26" s="57" t="n"/>
-      <c r="D26" s="57" t="n"/>
-      <c r="E26" s="57" t="n"/>
-      <c r="F26" s="57" t="n"/>
-      <c r="G26" s="57" t="n"/>
-      <c r="H26" s="57" t="n"/>
-      <c r="I26" s="57" t="n"/>
-      <c r="J26" s="58" t="n"/>
-      <c r="K26" s="79" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="L26" s="57" t="n"/>
-      <c r="M26" s="57" t="n"/>
-      <c r="N26" s="58" t="n"/>
-      <c r="O26" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P26" s="57" t="n"/>
-      <c r="Q26" s="57" t="n"/>
-      <c r="R26" s="58" t="n"/>
-    </row>
-    <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="80" t="inlineStr">
-        <is>
-          <t>R6 (Apr 2026)</t>
-        </is>
-      </c>
-      <c r="B27" s="81" t="inlineStr">
-        <is>
-          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C27" s="57" t="n"/>
-      <c r="D27" s="57" t="n"/>
-      <c r="E27" s="57" t="n"/>
-      <c r="F27" s="57" t="n"/>
-      <c r="G27" s="57" t="n"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="58" t="n"/>
-      <c r="K27" s="81" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="L27" s="57" t="n"/>
-      <c r="M27" s="57" t="n"/>
-      <c r="N27" s="58" t="n"/>
-      <c r="O27" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P27" s="57" t="n"/>
-      <c r="Q27" s="57" t="n"/>
-      <c r="R27" s="58" t="n"/>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="78" t="inlineStr">
-        <is>
-          <t>R7 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B28" s="79" t="inlineStr">
-        <is>
-          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C28" s="57" t="n"/>
-      <c r="D28" s="57" t="n"/>
-      <c r="E28" s="57" t="n"/>
-      <c r="F28" s="57" t="n"/>
-      <c r="G28" s="57" t="n"/>
-      <c r="H28" s="57" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="58" t="n"/>
-      <c r="K28" s="79" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="L28" s="57" t="n"/>
-      <c r="M28" s="57" t="n"/>
-      <c r="N28" s="58" t="n"/>
-      <c r="O28" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f13_a, f13_b</t>
-        </is>
-      </c>
-      <c r="P28" s="57" t="n"/>
-      <c r="Q28" s="57" t="n"/>
-      <c r="R28" s="58" t="n"/>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="80" t="inlineStr">
-        <is>
-          <t>R8 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B29" s="81" t="inlineStr">
-        <is>
-          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
-        </is>
-      </c>
-      <c r="C29" s="57" t="n"/>
-      <c r="D29" s="57" t="n"/>
-      <c r="E29" s="57" t="n"/>
-      <c r="F29" s="57" t="n"/>
-      <c r="G29" s="57" t="n"/>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="58" t="n"/>
-      <c r="K29" s="81" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="L29" s="57" t="n"/>
-      <c r="M29" s="57" t="n"/>
-      <c r="N29" s="58" t="n"/>
-      <c r="O29" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f1, f10, f13_a, f13_b, f14, f15, f16, f17, f18, f2, f3, f6, f7, f9</t>
-        </is>
-      </c>
-      <c r="P29" s="57" t="n"/>
-      <c r="Q29" s="57" t="n"/>
-      <c r="R29" s="58" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="A20:R20"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="B21:J21"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4242,7 +2781,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>M07 – Health  |  Cross-Round Variable Tracker  (R1–R5)</t>
+          <t>M06 – Finance  |  Cross-Round Variable Tracker  (R1–R5)</t>
         </is>
       </c>
     </row>
@@ -4364,1083 +2903,1044 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="71" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>WHETHER IT WAS NECESSARY TO GET HEALTH CARE SERVICES</t>
-        </is>
-      </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF HAVING A FORMAL BANK ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D4" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>Do you or anyone in your household own a formal bank account?</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr"/>
+      <c r="K4" s="33" t="inlineStr"/>
+      <c r="L4" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="37" t="inlineStr"/>
+      <c r="N4" s="72" t="inlineStr">
+        <is>
+          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr"/>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>Code 1: Go to F1; Code 2: Go to F18</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="inlineStr"/>
+      <c r="R4" s="37" t="inlineStr">
+        <is>
+          <t>Added in R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>WHETHER A HH MEMBER DEPOSITED MONEY IN A FORMAL BANK ACCOUNT IN THE P30D</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>All rounds</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H4" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>In the past 3 months, has it been necessary, for any reason, for any member of your HH to get health care services (i.e., consultation with doctor or any health care provider, diagnostic procedure, pr</t>
-        </is>
-      </c>
-      <c r="J4" s="27" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I5" s="68" t="inlineStr">
+        <is>
+          <t>Has anyone in your household received or deposited money into a formal bank account over the PAST MONTH?</t>
+        </is>
+      </c>
+      <c r="J5" s="68" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
       </c>
-      <c r="K4" s="23" t="n">
+      <c r="K5" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="68" t="inlineStr"/>
+      <c r="N5" s="68" t="inlineStr"/>
+      <c r="O5" s="68" t="inlineStr"/>
+      <c r="P5" s="68" t="inlineStr"/>
+      <c r="Q5" s="70" t="inlineStr">
+        <is>
+          <t>Ensure every household has a response (Yes/No).</t>
+        </is>
+      </c>
+      <c r="R5" s="68" t="inlineStr">
+        <is>
+          <t>Change samabahayan to sambahayan
+Revised Past 30 Days to Past Month to align with phrasing of Income module questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF HAVING A MOBILE MONEY ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>Do you or anyone in your household own a mobile money account such as Gcash, Maya, etc?</t>
+        </is>
+      </c>
+      <c r="J6" s="37" t="inlineStr"/>
+      <c r="K6" s="33" t="inlineStr"/>
+      <c r="L6" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="37" t="inlineStr"/>
+      <c r="N6" s="72" t="inlineStr">
+        <is>
+          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O6" s="37" t="inlineStr"/>
+      <c r="P6" s="37" t="inlineStr">
+        <is>
+          <t>Code 1: Go to F2; Code 2: Go to F3</t>
+        </is>
+      </c>
+      <c r="Q6" s="37" t="inlineStr"/>
+      <c r="R6" s="37" t="inlineStr">
+        <is>
+          <t>Added in R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>WHETHER A HH MEMBER RECEIVED/DEPOSITED MONEY INTO MOBILE BANKING SERVICE IN THE P30D</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="68" t="inlineStr">
+        <is>
+          <t>Has anyone in your household received or deposited money into Mobile Money service or an electronic wallet service over the PAST MONTH?</t>
+        </is>
+      </c>
+      <c r="J7" s="68" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K7" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="68" t="inlineStr"/>
+      <c r="N7" s="68" t="inlineStr"/>
+      <c r="O7" s="68" t="inlineStr"/>
+      <c r="P7" s="68" t="inlineStr"/>
+      <c r="Q7" s="68" t="inlineStr"/>
+      <c r="R7" s="68" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF SAVING SOME MONEY FOR THE FUTURE IN THE P30D</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I8" s="64" t="inlineStr">
+        <is>
+          <t>Given your financial commitments, were you able to save some money for the future over the PAST MONTH?</t>
+        </is>
+      </c>
+      <c r="J8" s="64" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="64" t="inlineStr"/>
+      <c r="N8" s="64" t="inlineStr"/>
+      <c r="O8" s="64" t="inlineStr"/>
+      <c r="P8" s="64" t="inlineStr"/>
+      <c r="Q8" s="64" t="inlineStr"/>
+      <c r="R8" s="64" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t>WHETHER HH CAN PAY AN EMERGENCY EXPENSE USING CASH, SAVINGS, OR OTHER RESOURCES ON HAND</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="68" t="inlineStr">
+        <is>
+          <t>Could your household currently pay an emergency expense of PhP50,000, using cash, savings, or other resources you have on-hand?</t>
+        </is>
+      </c>
+      <c r="J9" s="68" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K9" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="68" t="inlineStr"/>
+      <c r="N9" s="68" t="inlineStr"/>
+      <c r="O9" s="68" t="inlineStr"/>
+      <c r="P9" s="68" t="inlineStr"/>
+      <c r="Q9" s="68" t="inlineStr"/>
+      <c r="R9" s="68" t="inlineStr">
+        <is>
+          <t>Revised amount from 300k to 50k</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF APPLYING FOR CREDIT/LOAN IN THE P30D</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>Did you or any other member of your household apply or try to take on credit or a loan in the PAST MONTH?</t>
+        </is>
+      </c>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="27" t="inlineStr"/>
+      <c r="N10" s="72" t="inlineStr">
+        <is>
+          <t>Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O10" s="27" t="inlineStr">
+        <is>
+          <t>Code 1: Go to F8; Code 2: Go to F13; Code 98: Go to F13, Use "-"; Code 99: Go to F13</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>Code 1: Go to F8; Code 2: Go to F13; Code 98: Go to F13, Use "-"; Code 99: Go to F13</t>
+        </is>
+      </c>
+      <c r="Q10" s="27" t="inlineStr"/>
+      <c r="R10" s="27" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="66" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t>PURPOSE OF LOAN</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="68" t="inlineStr">
+        <is>
+          <t>For what purpose?</t>
+        </is>
+      </c>
+      <c r="J11" s="68" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K11" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" s="68" t="inlineStr"/>
+      <c r="N11" s="68" t="inlineStr"/>
+      <c r="O11" s="68" t="inlineStr"/>
+      <c r="P11" s="68" t="inlineStr"/>
+      <c r="Q11" s="70" t="inlineStr">
+        <is>
+          <t>Recode code 96</t>
+        </is>
+      </c>
+      <c r="R11" s="68" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>WHERE APPLIED FOR LOAN</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="64" t="inlineStr">
+        <is>
+          <t>To which institution or person did you or any other member of your household apply? (in the case of multiple, answer for the largest loan or credit)</t>
+        </is>
+      </c>
+      <c r="J12" s="64" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K12" s="65" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="65" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="64" t="inlineStr"/>
+      <c r="N12" s="64" t="inlineStr"/>
+      <c r="O12" s="64" t="inlineStr"/>
+      <c r="P12" s="64" t="inlineStr"/>
+      <c r="Q12" s="70" t="inlineStr">
+        <is>
+          <t>Recode code 96</t>
+        </is>
+      </c>
+      <c r="R12" s="64" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="66" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>WHETHER LOAN WAS APPROVED</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I13" s="68" t="inlineStr">
+        <is>
+          <t>Was the loan approved?</t>
+        </is>
+      </c>
+      <c r="J13" s="68" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K13" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="68" t="inlineStr"/>
+      <c r="N13" s="68" t="inlineStr"/>
+      <c r="O13" s="68" t="inlineStr"/>
+      <c r="P13" s="68" t="inlineStr"/>
+      <c r="Q13" s="68" t="inlineStr"/>
+      <c r="R13" s="68" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF USING MOBILE PHONE TO SEND MONEY</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I14" s="64" t="inlineStr">
+        <is>
+          <t>In the PAST MONTH, have you used a mobile phone to send money to someone else?</t>
+        </is>
+      </c>
+      <c r="J14" s="64" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K14" s="65" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="65" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="64" t="inlineStr"/>
+      <c r="N14" s="64" t="inlineStr"/>
+      <c r="O14" s="64" t="inlineStr"/>
+      <c r="P14" s="64" t="inlineStr"/>
+      <c r="Q14" s="64" t="inlineStr"/>
+      <c r="R14" s="64" t="inlineStr">
+        <is>
+          <t>Source: WB Findex 2021
+In the PAST 12 MONTHS, have you used a mobile phone to make payments, buy things, or to send or receive money?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF USING MOBILE PHONE TO BUY ONLINE</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="68" t="inlineStr">
+        <is>
+          <t>In the PAST MONTH, have you used a mobile phone to buy something online?</t>
+        </is>
+      </c>
+      <c r="J15" s="68" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K15" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="68" t="inlineStr"/>
+      <c r="N15" s="68" t="inlineStr"/>
+      <c r="O15" s="68" t="inlineStr"/>
+      <c r="P15" s="68" t="inlineStr"/>
+      <c r="Q15" s="68" t="inlineStr"/>
+      <c r="R15" s="68" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="B16" s="61" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF EXPERIENCING EITHER ATTEMPTED/SUCCESSFUL FRAUD/THEFT/OTHER FINANCIAL LOSS</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="64" t="inlineStr">
+        <is>
+          <t>In the PAST MONTH, have you or any household member experienced either attempted or successful fraud, theft, or other financial loss?</t>
+        </is>
+      </c>
+      <c r="J16" s="64" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K16" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="23" t="n">
+      <c r="L16" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="27" t="inlineStr"/>
-      <c r="N4" s="72" t="inlineStr">
-        <is>
-          <t>Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O4" s="27" t="inlineStr">
-        <is>
-          <t>Code 1: Go to H2A; Code 2: Go to H2A; Code 3: Go to H2A; Code 4: Go to H3</t>
-        </is>
-      </c>
-      <c r="P4" s="27" t="inlineStr">
-        <is>
-          <t>Code 1: Go to H2A; Code 2: Go to H2A; Code 3: Go to H2A; Code 4: Go to H3</t>
-        </is>
-      </c>
-      <c r="Q4" s="70" t="inlineStr">
-        <is>
-          <t>Must be filled for all household members</t>
-        </is>
-      </c>
-      <c r="R4" s="27" t="inlineStr">
-        <is>
-          <t>Please check Waray translation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="71" t="inlineStr">
-        <is>
-          <t>H2A</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>WHETHER WAS ABLE TO GET HEALTH CARE SERVICES</t>
-        </is>
-      </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="M16" s="64" t="inlineStr"/>
+      <c r="N16" s="64" t="inlineStr"/>
+      <c r="O16" s="64" t="inlineStr"/>
+      <c r="P16" s="64" t="inlineStr"/>
+      <c r="Q16" s="64" t="inlineStr"/>
+      <c r="R16" s="64" t="inlineStr">
+        <is>
+          <t>Source: L2Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr"/>
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>All rounds</t>
         </is>
       </c>
-      <c r="D5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H5" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>Were you or the member of your household able to get the health care services?</t>
-        </is>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="68" t="inlineStr"/>
+      <c r="J17" s="68" t="inlineStr"/>
+      <c r="K17" s="69" t="inlineStr"/>
+      <c r="L17" s="69" t="inlineStr"/>
+      <c r="M17" s="68" t="inlineStr"/>
+      <c r="N17" s="68" t="inlineStr"/>
+      <c r="O17" s="68" t="inlineStr"/>
+      <c r="P17" s="68" t="inlineStr"/>
+      <c r="Q17" s="68" t="inlineStr"/>
+      <c r="R17" s="68" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>WAYS OF RECEIVING REMITTANCES</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="64" t="inlineStr">
+        <is>
+          <t>In the PAST MONTH, have you or any member of your household RECEIVED remittances from family members or relatives who work in other city or other country in the following ways?</t>
+        </is>
+      </c>
+      <c r="J18" s="64" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
       </c>
-      <c r="K5" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="27" t="inlineStr"/>
-      <c r="N5" s="72" t="inlineStr">
-        <is>
-          <t>Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O5" s="27" t="inlineStr">
-        <is>
-          <t>Code 2: Go to H3</t>
-        </is>
-      </c>
-      <c r="P5" s="27" t="inlineStr">
-        <is>
-          <t>Code 2: Go to H3</t>
-        </is>
-      </c>
-      <c r="Q5" s="27" t="inlineStr"/>
-      <c r="R5" s="27" t="inlineStr"/>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="71" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>MAIN REASON FOR BEING UNABLE TO GET HEALTH CARE SERVICE</t>
-        </is>
-      </c>
-      <c r="C6" s="62" t="inlineStr">
-        <is>
-          <t>All rounds</t>
-        </is>
-      </c>
-      <c r="D6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H6" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I6" s="27" t="inlineStr">
-        <is>
-          <t>What was the main reason you or the member of your household were not able to get health care service?</t>
-        </is>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" s="27" t="inlineStr"/>
-      <c r="N6" s="72" t="inlineStr">
-        <is>
-          <t>Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O6" s="27" t="inlineStr">
-        <is>
-          <t>Code 96: Specify others. Limit answer to 100 characters only.</t>
-        </is>
-      </c>
-      <c r="P6" s="27" t="inlineStr">
-        <is>
-          <t>Code 96: Specify others. Limit answer to 100 characters only.</t>
-        </is>
-      </c>
-      <c r="Q6" s="27" t="inlineStr"/>
-      <c r="R6" s="27" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="73" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>MOST FREQUENT HEALTH CARE FACLITY VISITED</t>
-        </is>
-      </c>
-      <c r="C7" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D7" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>What type of facility or health care provider did you or your any member of your household visited most often for consultation/advice/care/treatment?</t>
-        </is>
-      </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K7" s="33" t="inlineStr"/>
-      <c r="L7" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" s="37" t="inlineStr"/>
-      <c r="N7" s="37" t="inlineStr"/>
-      <c r="O7" s="37" t="inlineStr"/>
-      <c r="P7" s="37" t="inlineStr"/>
-      <c r="Q7" s="37" t="inlineStr"/>
-      <c r="R7" s="37" t="inlineStr"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>USUAL AMOUNT SPENT ON TRANSPORTATION FOR CONSULTATION</t>
-        </is>
-      </c>
-      <c r="C8" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D8" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>How much do you or any member of your household usually spend on transportation to and from [HEALTH CARE FACILITY IN H4] for consultation?</t>
-        </is>
-      </c>
-      <c r="J8" s="37" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="K8" s="33" t="inlineStr"/>
-      <c r="L8" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="37" t="inlineStr"/>
-      <c r="N8" s="37" t="inlineStr"/>
-      <c r="O8" s="37" t="inlineStr"/>
-      <c r="P8" s="37" t="inlineStr"/>
-      <c r="Q8" s="37" t="inlineStr"/>
-      <c r="R8" s="37" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
-        <is>
-          <t>H8</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF PAYING OUT-OF-POCKET FOR CONSULTATION</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D9" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="inlineStr">
-        <is>
-          <t>Did you or any member of your household pay out-of-pocket (i.e., direct, household spending on health goods and services, without reimbursement from any health financing scheme) for consultation? If y</t>
-        </is>
-      </c>
-      <c r="J9" s="37" t="inlineStr">
-        <is>
-          <t>Categorical &amp; Numeric</t>
-        </is>
-      </c>
-      <c r="K9" s="33" t="inlineStr"/>
-      <c r="L9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" s="37" t="inlineStr"/>
-      <c r="N9" s="37" t="inlineStr"/>
-      <c r="O9" s="37" t="inlineStr"/>
-      <c r="P9" s="37" t="inlineStr"/>
-      <c r="Q9" s="37" t="inlineStr"/>
-      <c r="R9" s="37" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF BEING PRESCRIBED/ASKED TO GET SERVICES</t>
-        </is>
-      </c>
-      <c r="C10" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D10" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="37" t="inlineStr">
-        <is>
-          <t>Were you or any member of your household prescribed or asked to buy any of the following, or get the following services?</t>
-        </is>
-      </c>
-      <c r="J10" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K10" s="33" t="inlineStr"/>
-      <c r="L10" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="37" t="inlineStr"/>
-      <c r="N10" s="72" t="inlineStr">
-        <is>
-          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O10" s="37" t="inlineStr"/>
-      <c r="P10" s="37" t="inlineStr">
-        <is>
-          <t>Code 1: Go to H10; Code 2: Go to H12</t>
-        </is>
-      </c>
-      <c r="Q10" s="37" t="inlineStr"/>
-      <c r="R10" s="37" t="inlineStr"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="73" t="inlineStr">
-        <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF BEING ABLE TO BUY/GET PRESCRIBED SERVICE</t>
-        </is>
-      </c>
-      <c r="C11" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D11" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="37" t="inlineStr">
-        <is>
-          <t>Were you or the member of your household able to buy/ get [MENTION CODE 1 IN H9]?</t>
-        </is>
-      </c>
-      <c r="J11" s="37" t="inlineStr"/>
-      <c r="K11" s="33" t="inlineStr"/>
-      <c r="L11" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="37" t="inlineStr"/>
-      <c r="N11" s="72" t="inlineStr">
-        <is>
-          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O11" s="37" t="inlineStr"/>
-      <c r="P11" s="37" t="inlineStr">
-        <is>
-          <t>Code 1: Go to H11a; Code 2: Go to H12</t>
-        </is>
-      </c>
-      <c r="Q11" s="37" t="inlineStr"/>
-      <c r="R11" s="37" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="73" t="inlineStr">
-        <is>
-          <t>H11A</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>AMOUNT SPENT ON PRESCRIBED SERVICE</t>
-        </is>
-      </c>
-      <c r="C12" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D12" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I12" s="37" t="inlineStr">
-        <is>
-          <t>How much did you or the member of your household pay for [MENTION CODE 1 IN H9]?</t>
-        </is>
-      </c>
-      <c r="J12" s="37" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="K12" s="33" t="inlineStr"/>
-      <c r="L12" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="37" t="inlineStr"/>
-      <c r="N12" s="37" t="inlineStr"/>
-      <c r="O12" s="37" t="inlineStr"/>
-      <c r="P12" s="37" t="inlineStr"/>
-      <c r="Q12" s="37" t="inlineStr"/>
-      <c r="R12" s="37" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>H11B</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>WHO PAID FOR PRESCRIBED SERVICE</t>
-        </is>
-      </c>
-      <c r="C13" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D13" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I13" s="37" t="inlineStr">
-        <is>
-          <t>Who paid for [MENTION CODE 1 IN H9]?</t>
-        </is>
-      </c>
-      <c r="J13" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K13" s="33" t="inlineStr"/>
-      <c r="L13" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" s="37" t="inlineStr"/>
-      <c r="N13" s="37" t="inlineStr"/>
-      <c r="O13" s="37" t="inlineStr"/>
-      <c r="P13" s="37" t="inlineStr"/>
-      <c r="Q13" s="37" t="inlineStr"/>
-      <c r="R13" s="37" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="73" t="inlineStr">
-        <is>
-          <t>H12</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF BEING HOSPITALIZED</t>
-        </is>
-      </c>
-      <c r="C14" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D14" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>During the past 3 months, have you or any member of your household been hospitalized overnight for any reason?</t>
-        </is>
-      </c>
-      <c r="J14" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K14" s="33" t="inlineStr"/>
-      <c r="L14" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="37" t="inlineStr"/>
-      <c r="N14" s="72" t="inlineStr">
-        <is>
-          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
-        </is>
-      </c>
-      <c r="O14" s="37" t="inlineStr"/>
-      <c r="P14" s="37" t="inlineStr">
-        <is>
-          <t>Code 1: Go to H13; Code 2: Go to H17</t>
-        </is>
-      </c>
-      <c r="Q14" s="37" t="inlineStr"/>
-      <c r="R14" s="37" t="inlineStr"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>H13</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>TYPE OF HEALTH CARE FACILITY WHERE HOSPITALIZED</t>
-        </is>
-      </c>
-      <c r="C15" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D15" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I15" s="37" t="inlineStr">
-        <is>
-          <t>What type of hospital did  you or the member of your household receive treatment in the last time?</t>
-        </is>
-      </c>
-      <c r="J15" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K15" s="33" t="inlineStr"/>
-      <c r="L15" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="37" t="inlineStr"/>
-      <c r="N15" s="37" t="inlineStr"/>
-      <c r="O15" s="37" t="inlineStr"/>
-      <c r="P15" s="37" t="inlineStr"/>
-      <c r="Q15" s="37" t="inlineStr"/>
-      <c r="R15" s="37" t="inlineStr"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>H14</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>TOTAL HOSPITAL BILL</t>
-        </is>
-      </c>
-      <c r="C16" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D16" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I16" s="37" t="inlineStr">
-        <is>
-          <t>How much was the total bill?</t>
-        </is>
-      </c>
-      <c r="J16" s="37" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="K16" s="33" t="inlineStr"/>
-      <c r="L16" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="37" t="inlineStr"/>
-      <c r="N16" s="37" t="inlineStr"/>
-      <c r="O16" s="37" t="inlineStr"/>
-      <c r="P16" s="37" t="inlineStr"/>
-      <c r="Q16" s="37" t="inlineStr"/>
-      <c r="R16" s="37" t="inlineStr"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>H15</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>OUT-OF-POCKET EXPENSE ON HOSPITAL BILL</t>
-        </is>
-      </c>
-      <c r="C17" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D17" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I17" s="37" t="inlineStr">
-        <is>
-          <t>Of the total bill, how much did you or your immediate family pay out-of-pocket (i.e., direct, household spending on health goods and services, without reimbursement from any health financing scheme)?</t>
-        </is>
-      </c>
-      <c r="J17" s="37" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="K17" s="33" t="inlineStr"/>
-      <c r="L17" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="37" t="inlineStr"/>
-      <c r="N17" s="37" t="inlineStr"/>
-      <c r="O17" s="37" t="inlineStr"/>
-      <c r="P17" s="37" t="inlineStr"/>
-      <c r="Q17" s="37" t="inlineStr"/>
-      <c r="R17" s="37" t="inlineStr"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>H16</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>WHO PAID FOR THE REST OF HOSPITAL BILL</t>
-        </is>
-      </c>
-      <c r="C18" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>For the rest of the bill, who paid?</t>
-        </is>
-      </c>
-      <c r="J18" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K18" s="33" t="inlineStr"/>
-      <c r="L18" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="M18" s="37" t="inlineStr"/>
-      <c r="N18" s="37" t="inlineStr"/>
-      <c r="O18" s="37" t="inlineStr"/>
-      <c r="P18" s="37" t="inlineStr"/>
-      <c r="Q18" s="37" t="inlineStr"/>
-      <c r="R18" s="37" t="inlineStr"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="73" t="inlineStr">
-        <is>
-          <t>H17</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>INCIDENCE OF BEING A PHILHEALTH MEMBER &amp; WHETHER PAYING OR NOT PAYING</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="inlineStr">
-        <is>
-          <t>New in R5</t>
-        </is>
-      </c>
-      <c r="D19" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="63" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>Is [HH MEMBER, including OTHER HH MEMBERS] a member/dependent/beneficiary of PhilHealth?</t>
-        </is>
-      </c>
-      <c r="J19" s="37" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="K19" s="33" t="inlineStr"/>
-      <c r="L19" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="37" t="inlineStr"/>
-      <c r="N19" s="37" t="inlineStr"/>
-      <c r="O19" s="37" t="inlineStr"/>
-      <c r="P19" s="37" t="inlineStr"/>
-      <c r="Q19" s="37" t="inlineStr"/>
-      <c r="R19" s="37" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="K18" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="64" t="inlineStr"/>
+      <c r="N18" s="64" t="inlineStr"/>
+      <c r="O18" s="64" t="inlineStr"/>
+      <c r="P18" s="64" t="inlineStr"/>
+      <c r="Q18" s="64" t="inlineStr"/>
+      <c r="R18" s="64" t="inlineStr">
+        <is>
+          <t>Source: WB Findex 2021
+In the PAST 12 MONTHS, have you, personally, RECEIVED money from a relative or friend living in a different city or area inside (response in SA) in any of the following ways?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>DO-FILE VARIABLE DETAILS (destring/generate operations per round)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="77" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B22" s="77" t="inlineStr">
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>Variables processed (destring/tostring)</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="57" t="n"/>
+      <c r="F21" s="57" t="n"/>
+      <c r="G21" s="57" t="n"/>
+      <c r="H21" s="57" t="n"/>
+      <c r="I21" s="57" t="n"/>
+      <c r="J21" s="58" t="n"/>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="78" t="inlineStr">
+        <is>
+          <t>R1 (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C22" s="57" t="n"/>
@@ -5451,16 +3951,32 @@
       <c r="H22" s="57" t="n"/>
       <c r="I22" s="57" t="n"/>
       <c r="J22" s="58" t="n"/>
+      <c r="K22" s="79" t="inlineStr">
+        <is>
+          <t>f8_18, f8_24, f8_25</t>
+        </is>
+      </c>
+      <c r="L22" s="57" t="n"/>
+      <c r="M22" s="57" t="n"/>
+      <c r="N22" s="58" t="n"/>
+      <c r="O22" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
+        </is>
+      </c>
+      <c r="P22" s="57" t="n"/>
+      <c r="Q22" s="57" t="n"/>
+      <c r="R22" s="58" t="n"/>
     </row>
     <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="78" t="inlineStr">
-        <is>
-          <t>R1 (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="B23" s="79" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>R2 (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C23" s="57" t="n"/>
@@ -5471,13 +3987,13 @@
       <c r="H23" s="57" t="n"/>
       <c r="I23" s="57" t="n"/>
       <c r="J23" s="58" t="n"/>
-      <c r="K23" s="79" t="inlineStr"/>
+      <c r="K23" s="81" t="inlineStr"/>
       <c r="L23" s="57" t="n"/>
       <c r="M23" s="57" t="n"/>
       <c r="N23" s="58" t="n"/>
-      <c r="O23" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O23" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P23" s="57" t="n"/>
@@ -5485,14 +4001,14 @@
       <c r="R23" s="58" t="n"/>
     </row>
     <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="80" t="inlineStr">
-        <is>
-          <t>R2 (Dec 2025)</t>
-        </is>
-      </c>
-      <c r="B24" s="81" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>R3 (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="B24" s="79" t="inlineStr">
+        <is>
+          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C24" s="57" t="n"/>
@@ -5503,13 +4019,13 @@
       <c r="H24" s="57" t="n"/>
       <c r="I24" s="57" t="n"/>
       <c r="J24" s="58" t="n"/>
-      <c r="K24" s="81" t="inlineStr"/>
+      <c r="K24" s="79" t="inlineStr"/>
       <c r="L24" s="57" t="n"/>
       <c r="M24" s="57" t="n"/>
       <c r="N24" s="58" t="n"/>
-      <c r="O24" s="81" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O24" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P24" s="57" t="n"/>
@@ -5517,14 +4033,14 @@
       <c r="R24" s="58" t="n"/>
     </row>
     <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="78" t="inlineStr">
-        <is>
-          <t>R3 (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="B25" s="79" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>R4 (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="inlineStr">
+        <is>
+          <t>f1, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C25" s="57" t="n"/>
@@ -5535,13 +4051,13 @@
       <c r="H25" s="57" t="n"/>
       <c r="I25" s="57" t="n"/>
       <c r="J25" s="58" t="n"/>
-      <c r="K25" s="79" t="inlineStr"/>
+      <c r="K25" s="81" t="inlineStr"/>
       <c r="L25" s="57" t="n"/>
       <c r="M25" s="57" t="n"/>
       <c r="N25" s="58" t="n"/>
-      <c r="O25" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O25" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P25" s="57" t="n"/>
@@ -5549,14 +4065,14 @@
       <c r="R25" s="58" t="n"/>
     </row>
     <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="80" t="inlineStr">
-        <is>
-          <t>R4 (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="B26" s="81" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A26" s="78" t="inlineStr">
+        <is>
+          <t>R5 (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="B26" s="79" t="inlineStr">
+        <is>
+          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C26" s="57" t="n"/>
@@ -5567,13 +4083,17 @@
       <c r="H26" s="57" t="n"/>
       <c r="I26" s="57" t="n"/>
       <c r="J26" s="58" t="n"/>
-      <c r="K26" s="81" t="inlineStr"/>
+      <c r="K26" s="79" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
       <c r="L26" s="57" t="n"/>
       <c r="M26" s="57" t="n"/>
       <c r="N26" s="58" t="n"/>
-      <c r="O26" s="81" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O26" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P26" s="57" t="n"/>
@@ -5581,14 +4101,14 @@
       <c r="R26" s="58" t="n"/>
     </row>
     <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="78" t="inlineStr">
-        <is>
-          <t>R5 (Mar 2026)</t>
-        </is>
-      </c>
-      <c r="B27" s="79" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3, h4, h7, h8, h8_amt, h9a, h9b, h9c, h12, h13, h14, h15, h9_ans, h10, h11a</t>
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>R6 (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B27" s="81" t="inlineStr">
+        <is>
+          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C27" s="57" t="n"/>
@@ -5599,17 +4119,17 @@
       <c r="H27" s="57" t="n"/>
       <c r="I27" s="57" t="n"/>
       <c r="J27" s="58" t="n"/>
-      <c r="K27" s="79" t="inlineStr">
-        <is>
-          <t>health_index_str, round</t>
+      <c r="K27" s="81" t="inlineStr">
+        <is>
+          <t>round</t>
         </is>
       </c>
       <c r="L27" s="57" t="n"/>
       <c r="M27" s="57" t="n"/>
       <c r="N27" s="58" t="n"/>
-      <c r="O27" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: h8_amt, h9_ans, h9a, h9b, h9c</t>
+      <c r="O27" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P27" s="57" t="n"/>
@@ -5617,14 +4137,14 @@
       <c r="R27" s="58" t="n"/>
     </row>
     <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="80" t="inlineStr">
-        <is>
-          <t>R6 (Apr 2026)</t>
-        </is>
-      </c>
-      <c r="B28" s="81" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>R7 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B28" s="79" t="inlineStr">
+        <is>
+          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C28" s="57" t="n"/>
@@ -5635,7 +4155,7 @@
       <c r="H28" s="57" t="n"/>
       <c r="I28" s="57" t="n"/>
       <c r="J28" s="58" t="n"/>
-      <c r="K28" s="81" t="inlineStr">
+      <c r="K28" s="79" t="inlineStr">
         <is>
           <t>round</t>
         </is>
@@ -5643,9 +4163,9 @@
       <c r="L28" s="57" t="n"/>
       <c r="M28" s="57" t="n"/>
       <c r="N28" s="58" t="n"/>
-      <c r="O28" s="81" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O28" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P28" s="57" t="n"/>
@@ -5653,14 +4173,14 @@
       <c r="R28" s="58" t="n"/>
     </row>
     <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="78" t="inlineStr">
-        <is>
-          <t>R7 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B29" s="79" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3</t>
+      <c r="A29" s="80" t="inlineStr">
+        <is>
+          <t>R8 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B29" s="81" t="inlineStr">
+        <is>
+          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C29" s="57" t="n"/>
@@ -5671,7 +4191,7 @@
       <c r="H29" s="57" t="n"/>
       <c r="I29" s="57" t="n"/>
       <c r="J29" s="58" t="n"/>
-      <c r="K29" s="79" t="inlineStr">
+      <c r="K29" s="81" t="inlineStr">
         <is>
           <t>round</t>
         </is>
@@ -5679,9 +4199,9 @@
       <c r="L29" s="57" t="n"/>
       <c r="M29" s="57" t="n"/>
       <c r="N29" s="58" t="n"/>
-      <c r="O29" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
+      <c r="O29" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P29" s="57" t="n"/>
@@ -5689,14 +4209,14 @@
       <c r="R29" s="58" t="n"/>
     </row>
     <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="80" t="inlineStr">
-        <is>
-          <t>R8 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B30" s="81" t="inlineStr">
-        <is>
-          <t>h2, h2a, h3, h4, h7, h8, h8_amt, h9a, h9b, h9c, h12, h13, h14, h15, h9_ans, h10, h11a</t>
+      <c r="A30" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B30" s="79" t="inlineStr">
+        <is>
+          <t>f17, f1, f18, f2, f3, f6, f7, f9, f10, f13_a, f13_b, f14, f15, f16</t>
         </is>
       </c>
       <c r="C30" s="57" t="n"/>
@@ -5707,17 +4227,17 @@
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="57" t="n"/>
       <c r="J30" s="58" t="n"/>
-      <c r="K30" s="81" t="inlineStr">
-        <is>
-          <t>round, health_index_str, round</t>
+      <c r="K30" s="79" t="inlineStr">
+        <is>
+          <t>round</t>
         </is>
       </c>
       <c r="L30" s="57" t="n"/>
       <c r="M30" s="57" t="n"/>
       <c r="N30" s="58" t="n"/>
-      <c r="O30" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: h10, h11a, h12, h13, h14, h15, h2, h2a, h3, h4, h7, h8, h8_amt, h9_ans, h9a</t>
+      <c r="O30" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f13_a, f13_b</t>
         </is>
       </c>
       <c r="P30" s="57" t="n"/>
@@ -5725,13 +4245,12 @@
       <c r="R30" s="58" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="O23:R23"/>
     <mergeCell ref="K28:N28"/>
-    <mergeCell ref="A21:R21"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="D2:H2"/>
@@ -5742,7 +4261,9 @@
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="B24:J24"/>
     <mergeCell ref="B30:J30"/>
+    <mergeCell ref="A20:R20"/>
     <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K21:N21"/>
     <mergeCell ref="O30:R30"/>
     <mergeCell ref="K29:N29"/>
     <mergeCell ref="B26:J26"/>
@@ -5754,20 +4275,22 @@
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="O25:R25"/>
     <mergeCell ref="B27:J27"/>
+    <mergeCell ref="O21:R21"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="K27:N27"/>
+    <mergeCell ref="B21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5793,7 +4316,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>M08 – Food &amp; Non-Food  |  Cross-Round Variable Tracker  (R1–R5)</t>
+          <t>M07 – Health  |  Cross-Round Variable Tracker  (R1–R5)</t>
         </is>
       </c>
     </row>
@@ -5915,14 +4438,14 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
-        <is>
-          <t>F08</t>
-        </is>
-      </c>
-      <c r="B4" s="61" t="inlineStr">
-        <is>
-          <t>FOOD INSECURITY EXPERIENCE</t>
+      <c r="A4" s="71" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>WHETHER IT WAS NECESSARY TO GET HEALTH CARE SERVICES</t>
         </is>
       </c>
       <c r="C4" s="62" t="inlineStr">
@@ -5955,360 +4478,1409 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="64" t="inlineStr">
-        <is>
-          <t>Now I would like to ask you some questions about food . During the last 30 days, was there a time when any member of your household:</t>
-        </is>
-      </c>
-      <c r="J4" s="64" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>In the past 3 months, has it been necessary, for any reason, for any member of your HH to get health care services (i.e., consultation with doctor or any health care provider, diagnostic procedure, pr</t>
+        </is>
+      </c>
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
       </c>
-      <c r="K4" s="65" t="n">
+      <c r="K4" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="27" t="inlineStr"/>
+      <c r="N4" s="72" t="inlineStr">
+        <is>
+          <t>Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O4" s="27" t="inlineStr">
+        <is>
+          <t>Code 1: Go to H2A; Code 2: Go to H2A; Code 3: Go to H2A; Code 4: Go to H3</t>
+        </is>
+      </c>
+      <c r="P4" s="27" t="inlineStr">
+        <is>
+          <t>Code 1: Go to H2A; Code 2: Go to H2A; Code 3: Go to H2A; Code 4: Go to H3</t>
+        </is>
+      </c>
+      <c r="Q4" s="70" t="inlineStr">
+        <is>
+          <t>Must be filled for all household members</t>
+        </is>
+      </c>
+      <c r="R4" s="27" t="inlineStr">
+        <is>
+          <t>Please check Waray translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="71" t="inlineStr">
+        <is>
+          <t>H2A</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>WHETHER WAS ABLE TO GET HEALTH CARE SERVICES</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>Were you or the member of your household able to get the health care services?</t>
+        </is>
+      </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="27" t="inlineStr"/>
+      <c r="N5" s="72" t="inlineStr">
+        <is>
+          <t>Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>Code 2: Go to H3</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>Code 2: Go to H3</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr"/>
+      <c r="R5" s="27" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="71" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>MAIN REASON FOR BEING UNABLE TO GET HEALTH CARE SERVICE</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="inlineStr">
+        <is>
+          <t>What was the main reason you or the member of your household were not able to get health care service?</t>
+        </is>
+      </c>
+      <c r="J6" s="27" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" s="27" t="inlineStr"/>
+      <c r="N6" s="72" t="inlineStr">
+        <is>
+          <t>Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t>Code 96: Specify others. Limit answer to 100 characters only.</t>
+        </is>
+      </c>
+      <c r="P6" s="27" t="inlineStr">
+        <is>
+          <t>Code 96: Specify others. Limit answer to 100 characters only.</t>
+        </is>
+      </c>
+      <c r="Q6" s="27" t="inlineStr"/>
+      <c r="R6" s="27" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>MOST FREQUENT HEALTH CARE FACLITY VISITED</t>
+        </is>
+      </c>
+      <c r="C7" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>What type of facility or health care provider did you or your any member of your household visited most often for consultation/advice/care/treatment?</t>
+        </is>
+      </c>
+      <c r="J7" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr"/>
+      <c r="L7" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="37" t="inlineStr"/>
+      <c r="N7" s="37" t="inlineStr"/>
+      <c r="O7" s="37" t="inlineStr"/>
+      <c r="P7" s="37" t="inlineStr"/>
+      <c r="Q7" s="37" t="inlineStr"/>
+      <c r="R7" s="37" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>USUAL AMOUNT SPENT ON TRANSPORTATION FOR CONSULTATION</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I8" s="37" t="inlineStr">
+        <is>
+          <t>How much do you or any member of your household usually spend on transportation to and from [HEALTH CARE FACILITY IN H4] for consultation?</t>
+        </is>
+      </c>
+      <c r="J8" s="37" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="K8" s="33" t="inlineStr"/>
+      <c r="L8" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="37" t="inlineStr"/>
+      <c r="N8" s="37" t="inlineStr"/>
+      <c r="O8" s="37" t="inlineStr"/>
+      <c r="P8" s="37" t="inlineStr"/>
+      <c r="Q8" s="37" t="inlineStr"/>
+      <c r="R8" s="37" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
+          <t>H8</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF PAYING OUT-OF-POCKET FOR CONSULTATION</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="37" t="inlineStr">
+        <is>
+          <t>Did you or any member of your household pay out-of-pocket (i.e., direct, household spending on health goods and services, without reimbursement from any health financing scheme) for consultation? If y</t>
+        </is>
+      </c>
+      <c r="J9" s="37" t="inlineStr">
+        <is>
+          <t>Categorical &amp; Numeric</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr"/>
+      <c r="L9" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="37" t="inlineStr"/>
+      <c r="N9" s="37" t="inlineStr"/>
+      <c r="O9" s="37" t="inlineStr"/>
+      <c r="P9" s="37" t="inlineStr"/>
+      <c r="Q9" s="37" t="inlineStr"/>
+      <c r="R9" s="37" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF BEING PRESCRIBED/ASKED TO GET SERVICES</t>
+        </is>
+      </c>
+      <c r="C10" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Were you or any member of your household prescribed or asked to buy any of the following, or get the following services?</t>
+        </is>
+      </c>
+      <c r="J10" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr"/>
+      <c r="L10" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="37" t="inlineStr"/>
+      <c r="N10" s="72" t="inlineStr">
+        <is>
+          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O10" s="37" t="inlineStr"/>
+      <c r="P10" s="37" t="inlineStr">
+        <is>
+          <t>Code 1: Go to H10; Code 2: Go to H12</t>
+        </is>
+      </c>
+      <c r="Q10" s="37" t="inlineStr"/>
+      <c r="R10" s="37" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="73" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF BEING ABLE TO BUY/GET PRESCRIBED SERVICE</t>
+        </is>
+      </c>
+      <c r="C11" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="37" t="inlineStr">
+        <is>
+          <t>Were you or the member of your household able to buy/ get [MENTION CODE 1 IN H9]?</t>
+        </is>
+      </c>
+      <c r="J11" s="37" t="inlineStr"/>
+      <c r="K11" s="33" t="inlineStr"/>
+      <c r="L11" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="65" t="n">
+      <c r="M11" s="37" t="inlineStr"/>
+      <c r="N11" s="72" t="inlineStr">
+        <is>
+          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O11" s="37" t="inlineStr"/>
+      <c r="P11" s="37" t="inlineStr">
+        <is>
+          <t>Code 1: Go to H11a; Code 2: Go to H12</t>
+        </is>
+      </c>
+      <c r="Q11" s="37" t="inlineStr"/>
+      <c r="R11" s="37" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>H11A</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>AMOUNT SPENT ON PRESCRIBED SERVICE</t>
+        </is>
+      </c>
+      <c r="C12" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>How much did you or the member of your household pay for [MENTION CODE 1 IN H9]?</t>
+        </is>
+      </c>
+      <c r="J12" s="37" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="K12" s="33" t="inlineStr"/>
+      <c r="L12" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37" t="inlineStr"/>
+      <c r="N12" s="37" t="inlineStr"/>
+      <c r="O12" s="37" t="inlineStr"/>
+      <c r="P12" s="37" t="inlineStr"/>
+      <c r="Q12" s="37" t="inlineStr"/>
+      <c r="R12" s="37" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>H11B</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>WHO PAID FOR PRESCRIBED SERVICE</t>
+        </is>
+      </c>
+      <c r="C13" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="inlineStr">
+        <is>
+          <t>Who paid for [MENTION CODE 1 IN H9]?</t>
+        </is>
+      </c>
+      <c r="J13" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K13" s="33" t="inlineStr"/>
+      <c r="L13" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="37" t="inlineStr"/>
+      <c r="N13" s="37" t="inlineStr"/>
+      <c r="O13" s="37" t="inlineStr"/>
+      <c r="P13" s="37" t="inlineStr"/>
+      <c r="Q13" s="37" t="inlineStr"/>
+      <c r="R13" s="37" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF BEING HOSPITALIZED</t>
+        </is>
+      </c>
+      <c r="C14" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D14" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>During the past 3 months, have you or any member of your household been hospitalized overnight for any reason?</t>
+        </is>
+      </c>
+      <c r="J14" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K14" s="33" t="inlineStr"/>
+      <c r="L14" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="M4" s="64" t="inlineStr"/>
-      <c r="N4" s="64" t="inlineStr"/>
-      <c r="O4" s="64" t="inlineStr"/>
-      <c r="P4" s="64" t="inlineStr"/>
-      <c r="Q4" s="64" t="inlineStr"/>
-      <c r="R4" s="64" t="inlineStr">
-        <is>
-          <t>As per Sharon, retained previous phrasing of questoin following the FAO guidelines on the FIES (Food Insecurity Experience Scale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr"/>
+      <c r="N14" s="72" t="inlineStr">
+        <is>
+          <t>Added in R5 | Changed R5→R6 | Changed R6→R7</t>
+        </is>
+      </c>
+      <c r="O14" s="37" t="inlineStr"/>
+      <c r="P14" s="37" t="inlineStr">
+        <is>
+          <t>Code 1: Go to H13; Code 2: Go to H17</t>
+        </is>
+      </c>
+      <c r="Q14" s="37" t="inlineStr"/>
+      <c r="R14" s="37" t="inlineStr"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>TYPE OF HEALTH CARE FACILITY WHERE HOSPITALIZED</t>
+        </is>
+      </c>
+      <c r="C15" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D15" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>What type of hospital did  you or the member of your household receive treatment in the last time?</t>
+        </is>
+      </c>
+      <c r="J15" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K15" s="33" t="inlineStr"/>
+      <c r="L15" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="37" t="inlineStr"/>
+      <c r="N15" s="37" t="inlineStr"/>
+      <c r="O15" s="37" t="inlineStr"/>
+      <c r="P15" s="37" t="inlineStr"/>
+      <c r="Q15" s="37" t="inlineStr"/>
+      <c r="R15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>TOTAL HOSPITAL BILL</t>
+        </is>
+      </c>
+      <c r="C16" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D16" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>How much was the total bill?</t>
+        </is>
+      </c>
+      <c r="J16" s="37" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="K16" s="33" t="inlineStr"/>
+      <c r="L16" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37" t="inlineStr"/>
+      <c r="N16" s="37" t="inlineStr"/>
+      <c r="O16" s="37" t="inlineStr"/>
+      <c r="P16" s="37" t="inlineStr"/>
+      <c r="Q16" s="37" t="inlineStr"/>
+      <c r="R16" s="37" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>OUT-OF-POCKET EXPENSE ON HOSPITAL BILL</t>
+        </is>
+      </c>
+      <c r="C17" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D17" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="37" t="inlineStr">
+        <is>
+          <t>Of the total bill, how much did you or your immediate family pay out-of-pocket (i.e., direct, household spending on health goods and services, without reimbursement from any health financing scheme)?</t>
+        </is>
+      </c>
+      <c r="J17" s="37" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="K17" s="33" t="inlineStr"/>
+      <c r="L17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37" t="inlineStr"/>
+      <c r="N17" s="37" t="inlineStr"/>
+      <c r="O17" s="37" t="inlineStr"/>
+      <c r="P17" s="37" t="inlineStr"/>
+      <c r="Q17" s="37" t="inlineStr"/>
+      <c r="R17" s="37" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>WHO PAID FOR THE REST OF HOSPITAL BILL</t>
+        </is>
+      </c>
+      <c r="C18" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>For the rest of the bill, who paid?</t>
+        </is>
+      </c>
+      <c r="J18" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K18" s="33" t="inlineStr"/>
+      <c r="L18" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" s="37" t="inlineStr"/>
+      <c r="N18" s="37" t="inlineStr"/>
+      <c r="O18" s="37" t="inlineStr"/>
+      <c r="P18" s="37" t="inlineStr"/>
+      <c r="Q18" s="37" t="inlineStr"/>
+      <c r="R18" s="37" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>H17</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF BEING A PHILHEALTH MEMBER &amp; WHETHER PAYING OR NOT PAYING</t>
+        </is>
+      </c>
+      <c r="C19" s="74" t="inlineStr">
+        <is>
+          <t>New in R5</t>
+        </is>
+      </c>
+      <c r="D19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>Is [HH MEMBER, including OTHER HH MEMBERS] a member/dependent/beneficiary of PhilHealth?</t>
+        </is>
+      </c>
+      <c r="J19" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K19" s="33" t="inlineStr"/>
+      <c r="L19" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="37" t="inlineStr"/>
+      <c r="N19" s="37" t="inlineStr"/>
+      <c r="O19" s="37" t="inlineStr"/>
+      <c r="P19" s="37" t="inlineStr"/>
+      <c r="Q19" s="37" t="inlineStr"/>
+      <c r="R19" s="37" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>DO-FILE VARIABLE DETAILS (destring/generate operations per round)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="77" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="77" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t>Variables processed (destring/tostring)</t>
         </is>
       </c>
-      <c r="C7" s="57" t="n"/>
-      <c r="D7" s="57" t="n"/>
-      <c r="E7" s="57" t="n"/>
-      <c r="F7" s="57" t="n"/>
-      <c r="G7" s="57" t="n"/>
-      <c r="H7" s="57" t="n"/>
-      <c r="I7" s="57" t="n"/>
-      <c r="J7" s="58" t="n"/>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="57" t="n"/>
+      <c r="E22" s="57" t="n"/>
+      <c r="F22" s="57" t="n"/>
+      <c r="G22" s="57" t="n"/>
+      <c r="H22" s="57" t="n"/>
+      <c r="I22" s="57" t="n"/>
+      <c r="J22" s="58" t="n"/>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="78" t="inlineStr">
         <is>
           <t>R1 (Nov 2025)</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="C8" s="57" t="n"/>
-      <c r="D8" s="57" t="n"/>
-      <c r="E8" s="57" t="n"/>
-      <c r="F8" s="57" t="n"/>
-      <c r="G8" s="57" t="n"/>
-      <c r="H8" s="57" t="n"/>
-      <c r="I8" s="57" t="n"/>
-      <c r="J8" s="58" t="n"/>
-      <c r="K8" s="79" t="inlineStr"/>
-      <c r="L8" s="57" t="n"/>
-      <c r="M8" s="57" t="n"/>
-      <c r="N8" s="58" t="n"/>
-      <c r="O8" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="P8" s="57" t="n"/>
-      <c r="Q8" s="57" t="n"/>
-      <c r="R8" s="58" t="n"/>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="80" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="n"/>
+      <c r="D23" s="57" t="n"/>
+      <c r="E23" s="57" t="n"/>
+      <c r="F23" s="57" t="n"/>
+      <c r="G23" s="57" t="n"/>
+      <c r="H23" s="57" t="n"/>
+      <c r="I23" s="57" t="n"/>
+      <c r="J23" s="58" t="n"/>
+      <c r="K23" s="79" t="inlineStr"/>
+      <c r="L23" s="57" t="n"/>
+      <c r="M23" s="57" t="n"/>
+      <c r="N23" s="58" t="n"/>
+      <c r="O23" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P23" s="57" t="n"/>
+      <c r="Q23" s="57" t="n"/>
+      <c r="R23" s="58" t="n"/>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="80" t="inlineStr">
         <is>
           <t>R2 (Dec 2025)</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="C9" s="57" t="n"/>
-      <c r="D9" s="57" t="n"/>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="57" t="n"/>
-      <c r="H9" s="57" t="n"/>
-      <c r="I9" s="57" t="n"/>
-      <c r="J9" s="58" t="n"/>
-      <c r="K9" s="81" t="inlineStr"/>
-      <c r="L9" s="57" t="n"/>
-      <c r="M9" s="57" t="n"/>
-      <c r="N9" s="58" t="n"/>
-      <c r="O9" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="P9" s="57" t="n"/>
-      <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="58" t="n"/>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="n"/>
+      <c r="D24" s="57" t="n"/>
+      <c r="E24" s="57" t="n"/>
+      <c r="F24" s="57" t="n"/>
+      <c r="G24" s="57" t="n"/>
+      <c r="H24" s="57" t="n"/>
+      <c r="I24" s="57" t="n"/>
+      <c r="J24" s="58" t="n"/>
+      <c r="K24" s="81" t="inlineStr"/>
+      <c r="L24" s="57" t="n"/>
+      <c r="M24" s="57" t="n"/>
+      <c r="N24" s="58" t="n"/>
+      <c r="O24" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P24" s="57" t="n"/>
+      <c r="Q24" s="57" t="n"/>
+      <c r="R24" s="58" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>R3 (Jan 2026)</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="57" t="n"/>
-      <c r="H10" s="57" t="n"/>
-      <c r="I10" s="57" t="n"/>
-      <c r="J10" s="58" t="n"/>
-      <c r="K10" s="79" t="inlineStr"/>
-      <c r="L10" s="57" t="n"/>
-      <c r="M10" s="57" t="n"/>
-      <c r="N10" s="58" t="n"/>
-      <c r="O10" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="P10" s="57" t="n"/>
-      <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="58" t="n"/>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="80" t="inlineStr">
+      <c r="B25" s="79" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="57" t="n"/>
+      <c r="F25" s="57" t="n"/>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="57" t="n"/>
+      <c r="I25" s="57" t="n"/>
+      <c r="J25" s="58" t="n"/>
+      <c r="K25" s="79" t="inlineStr"/>
+      <c r="L25" s="57" t="n"/>
+      <c r="M25" s="57" t="n"/>
+      <c r="N25" s="58" t="n"/>
+      <c r="O25" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P25" s="57" t="n"/>
+      <c r="Q25" s="57" t="n"/>
+      <c r="R25" s="58" t="n"/>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>R4 (Feb 2026)</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-      <c r="I11" s="57" t="n"/>
-      <c r="J11" s="58" t="n"/>
-      <c r="K11" s="81" t="inlineStr"/>
-      <c r="L11" s="57" t="n"/>
-      <c r="M11" s="57" t="n"/>
-      <c r="N11" s="58" t="n"/>
-      <c r="O11" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="P11" s="57" t="n"/>
-      <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="58" t="n"/>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="57" t="n"/>
+      <c r="F26" s="57" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n"/>
+      <c r="I26" s="57" t="n"/>
+      <c r="J26" s="58" t="n"/>
+      <c r="K26" s="81" t="inlineStr"/>
+      <c r="L26" s="57" t="n"/>
+      <c r="M26" s="57" t="n"/>
+      <c r="N26" s="58" t="n"/>
+      <c r="O26" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P26" s="57" t="n"/>
+      <c r="Q26" s="57" t="n"/>
+      <c r="R26" s="58" t="n"/>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="78" t="inlineStr">
         <is>
           <t>R5 (Mar 2026)</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="57" t="n"/>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="57" t="n"/>
-      <c r="H12" s="57" t="n"/>
-      <c r="I12" s="57" t="n"/>
-      <c r="J12" s="58" t="n"/>
-      <c r="K12" s="79" t="inlineStr"/>
-      <c r="L12" s="57" t="n"/>
-      <c r="M12" s="57" t="n"/>
-      <c r="N12" s="58" t="n"/>
-      <c r="O12" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
-        </is>
-      </c>
-      <c r="P12" s="57" t="n"/>
-      <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="58" t="n"/>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="B27" s="79" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3, h4, h7, h8, h8_amt, h9a, h9b, h9c, h12, h13, h14, h15, h9_ans, h10, h11a</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="n"/>
+      <c r="D27" s="57" t="n"/>
+      <c r="E27" s="57" t="n"/>
+      <c r="F27" s="57" t="n"/>
+      <c r="G27" s="57" t="n"/>
+      <c r="H27" s="57" t="n"/>
+      <c r="I27" s="57" t="n"/>
+      <c r="J27" s="58" t="n"/>
+      <c r="K27" s="79" t="inlineStr">
+        <is>
+          <t>health_index_str, round</t>
+        </is>
+      </c>
+      <c r="L27" s="57" t="n"/>
+      <c r="M27" s="57" t="n"/>
+      <c r="N27" s="58" t="n"/>
+      <c r="O27" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: h8_amt, h9_ans, h9a, h9b, h9c</t>
+        </is>
+      </c>
+      <c r="P27" s="57" t="n"/>
+      <c r="Q27" s="57" t="n"/>
+      <c r="R27" s="58" t="n"/>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="80" t="inlineStr">
         <is>
           <t>R6 (Apr 2026)</t>
         </is>
       </c>
-      <c r="B13" s="81" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="C13" s="57" t="n"/>
-      <c r="D13" s="57" t="n"/>
-      <c r="E13" s="57" t="n"/>
-      <c r="F13" s="57" t="n"/>
-      <c r="G13" s="57" t="n"/>
-      <c r="H13" s="57" t="n"/>
-      <c r="I13" s="57" t="n"/>
-      <c r="J13" s="58" t="n"/>
-      <c r="K13" s="81" t="inlineStr"/>
-      <c r="L13" s="57" t="n"/>
-      <c r="M13" s="57" t="n"/>
-      <c r="N13" s="58" t="n"/>
-      <c r="O13" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="P13" s="57" t="n"/>
-      <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="58" t="n"/>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="B28" s="81" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="n"/>
+      <c r="D28" s="57" t="n"/>
+      <c r="E28" s="57" t="n"/>
+      <c r="F28" s="57" t="n"/>
+      <c r="G28" s="57" t="n"/>
+      <c r="H28" s="57" t="n"/>
+      <c r="I28" s="57" t="n"/>
+      <c r="J28" s="58" t="n"/>
+      <c r="K28" s="81" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="L28" s="57" t="n"/>
+      <c r="M28" s="57" t="n"/>
+      <c r="N28" s="58" t="n"/>
+      <c r="O28" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P28" s="57" t="n"/>
+      <c r="Q28" s="57" t="n"/>
+      <c r="R28" s="58" t="n"/>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="78" t="inlineStr">
         <is>
           <t>R7 (May 2026)</t>
         </is>
       </c>
-      <c r="B14" s="79" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="C14" s="57" t="n"/>
-      <c r="D14" s="57" t="n"/>
-      <c r="E14" s="57" t="n"/>
-      <c r="F14" s="57" t="n"/>
-      <c r="G14" s="57" t="n"/>
-      <c r="H14" s="57" t="n"/>
-      <c r="I14" s="57" t="n"/>
-      <c r="J14" s="58" t="n"/>
-      <c r="K14" s="79" t="inlineStr"/>
-      <c r="L14" s="57" t="n"/>
-      <c r="M14" s="57" t="n"/>
-      <c r="N14" s="58" t="n"/>
-      <c r="O14" s="82" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="P14" s="57" t="n"/>
-      <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="58" t="n"/>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="80" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="57" t="n"/>
+      <c r="F29" s="57" t="n"/>
+      <c r="G29" s="57" t="n"/>
+      <c r="H29" s="57" t="n"/>
+      <c r="I29" s="57" t="n"/>
+      <c r="J29" s="58" t="n"/>
+      <c r="K29" s="79" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="L29" s="57" t="n"/>
+      <c r="M29" s="57" t="n"/>
+      <c r="N29" s="58" t="n"/>
+      <c r="O29" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P29" s="57" t="n"/>
+      <c r="Q29" s="57" t="n"/>
+      <c r="R29" s="58" t="n"/>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="80" t="inlineStr">
         <is>
           <t>R8 (Jun 2026)</t>
         </is>
       </c>
-      <c r="B15" s="81" t="inlineStr">
-        <is>
-          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="C15" s="57" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="57" t="n"/>
-      <c r="H15" s="57" t="n"/>
-      <c r="I15" s="57" t="n"/>
-      <c r="J15" s="58" t="n"/>
-      <c r="K15" s="81" t="inlineStr"/>
-      <c r="L15" s="57" t="n"/>
-      <c r="M15" s="57" t="n"/>
-      <c r="N15" s="58" t="n"/>
-      <c r="O15" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
-        </is>
-      </c>
-      <c r="P15" s="57" t="n"/>
-      <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="58" t="n"/>
+      <c r="B30" s="81" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3, h4, h7, h8, h8_amt, h9a, h9b, h9c, h12, h13, h14, h15, h9_ans, h10, h11a</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="n"/>
+      <c r="D30" s="57" t="n"/>
+      <c r="E30" s="57" t="n"/>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="57" t="n"/>
+      <c r="I30" s="57" t="n"/>
+      <c r="J30" s="58" t="n"/>
+      <c r="K30" s="81" t="inlineStr">
+        <is>
+          <t>round, health_index_str, round</t>
+        </is>
+      </c>
+      <c r="L30" s="57" t="n"/>
+      <c r="M30" s="57" t="n"/>
+      <c r="N30" s="58" t="n"/>
+      <c r="O30" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: h8_amt, h9_ans, h9a, h9b, h9c</t>
+        </is>
+      </c>
+      <c r="P30" s="57" t="n"/>
+      <c r="Q30" s="57" t="n"/>
+      <c r="R30" s="58" t="n"/>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B31" s="79" t="inlineStr">
+        <is>
+          <t>h2, h2a, h3</t>
+        </is>
+      </c>
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="57" t="n"/>
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="57" t="n"/>
+      <c r="I31" s="57" t="n"/>
+      <c r="J31" s="58" t="n"/>
+      <c r="K31" s="79" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="L31" s="57" t="n"/>
+      <c r="M31" s="57" t="n"/>
+      <c r="N31" s="58" t="n"/>
+      <c r="O31" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P31" s="57" t="n"/>
+      <c r="Q31" s="57" t="n"/>
+      <c r="R31" s="58" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="O13:R13"/>
+  <mergeCells count="33">
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="A21:R21"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B28:J28"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="K27:N27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6334,7 +5906,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>M09 – Opinions &amp; Views  |  Cross-Round Variable Tracker  (R1–R5)</t>
+          <t>M08 – Food &amp; Non-Food  |  Cross-Round Variable Tracker  (R1–R5)</t>
         </is>
       </c>
     </row>
@@ -6458,6 +6030,582 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="60" t="inlineStr">
         <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>FOOD INSECURITY EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="C4" s="62" t="inlineStr">
+        <is>
+          <t>All rounds</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I4" s="64" t="inlineStr">
+        <is>
+          <t>Now I would like to ask you some questions about food . During the last 30 days, was there a time when any member of your household:</t>
+        </is>
+      </c>
+      <c r="J4" s="64" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K4" s="65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="64" t="inlineStr"/>
+      <c r="N4" s="64" t="inlineStr"/>
+      <c r="O4" s="64" t="inlineStr"/>
+      <c r="P4" s="64" t="inlineStr"/>
+      <c r="Q4" s="64" t="inlineStr"/>
+      <c r="R4" s="64" t="inlineStr">
+        <is>
+          <t>As per Sharon, retained previous phrasing of questoin following the FAO guidelines on the FIES (Food Insecurity Experience Scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="76" t="inlineStr">
+        <is>
+          <t>DO-FILE VARIABLE DETAILS (destring/generate operations per round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="77" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>Variables processed (destring/tostring)</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="n"/>
+      <c r="D7" s="57" t="n"/>
+      <c r="E7" s="57" t="n"/>
+      <c r="F7" s="57" t="n"/>
+      <c r="G7" s="57" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="57" t="n"/>
+      <c r="J7" s="58" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="78" t="inlineStr">
+        <is>
+          <t>R1 (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="B8" s="79" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="C8" s="57" t="n"/>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="57" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="57" t="n"/>
+      <c r="H8" s="57" t="n"/>
+      <c r="I8" s="57" t="n"/>
+      <c r="J8" s="58" t="n"/>
+      <c r="K8" s="79" t="inlineStr"/>
+      <c r="L8" s="57" t="n"/>
+      <c r="M8" s="57" t="n"/>
+      <c r="N8" s="58" t="n"/>
+      <c r="O8" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="P8" s="57" t="n"/>
+      <c r="Q8" s="57" t="n"/>
+      <c r="R8" s="58" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>R2 (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="57" t="n"/>
+      <c r="F9" s="57" t="n"/>
+      <c r="G9" s="57" t="n"/>
+      <c r="H9" s="57" t="n"/>
+      <c r="I9" s="57" t="n"/>
+      <c r="J9" s="58" t="n"/>
+      <c r="K9" s="81" t="inlineStr"/>
+      <c r="L9" s="57" t="n"/>
+      <c r="M9" s="57" t="n"/>
+      <c r="N9" s="58" t="n"/>
+      <c r="O9" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="P9" s="57" t="n"/>
+      <c r="Q9" s="57" t="n"/>
+      <c r="R9" s="58" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="78" t="inlineStr">
+        <is>
+          <t>R3 (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="n"/>
+      <c r="D10" s="57" t="n"/>
+      <c r="E10" s="57" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="57" t="n"/>
+      <c r="H10" s="57" t="n"/>
+      <c r="I10" s="57" t="n"/>
+      <c r="J10" s="58" t="n"/>
+      <c r="K10" s="79" t="inlineStr"/>
+      <c r="L10" s="57" t="n"/>
+      <c r="M10" s="57" t="n"/>
+      <c r="N10" s="58" t="n"/>
+      <c r="O10" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="P10" s="57" t="n"/>
+      <c r="Q10" s="57" t="n"/>
+      <c r="R10" s="58" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>R4 (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="57" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
+      <c r="I11" s="57" t="n"/>
+      <c r="J11" s="58" t="n"/>
+      <c r="K11" s="81" t="inlineStr"/>
+      <c r="L11" s="57" t="n"/>
+      <c r="M11" s="57" t="n"/>
+      <c r="N11" s="58" t="n"/>
+      <c r="O11" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="P11" s="57" t="n"/>
+      <c r="Q11" s="57" t="n"/>
+      <c r="R11" s="58" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="78" t="inlineStr">
+        <is>
+          <t>R5 (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
+      <c r="I12" s="57" t="n"/>
+      <c r="J12" s="58" t="n"/>
+      <c r="K12" s="79" t="inlineStr"/>
+      <c r="L12" s="57" t="n"/>
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="58" t="n"/>
+      <c r="O12" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e</t>
+        </is>
+      </c>
+      <c r="P12" s="57" t="n"/>
+      <c r="Q12" s="57" t="n"/>
+      <c r="R12" s="58" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>R6 (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="C13" s="57" t="n"/>
+      <c r="D13" s="57" t="n"/>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="57" t="n"/>
+      <c r="G13" s="57" t="n"/>
+      <c r="H13" s="57" t="n"/>
+      <c r="I13" s="57" t="n"/>
+      <c r="J13" s="58" t="n"/>
+      <c r="K13" s="81" t="inlineStr"/>
+      <c r="L13" s="57" t="n"/>
+      <c r="M13" s="57" t="n"/>
+      <c r="N13" s="58" t="n"/>
+      <c r="O13" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="P13" s="57" t="n"/>
+      <c r="Q13" s="57" t="n"/>
+      <c r="R13" s="58" t="n"/>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="78" t="inlineStr">
+        <is>
+          <t>R7 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="C14" s="57" t="n"/>
+      <c r="D14" s="57" t="n"/>
+      <c r="E14" s="57" t="n"/>
+      <c r="F14" s="57" t="n"/>
+      <c r="G14" s="57" t="n"/>
+      <c r="H14" s="57" t="n"/>
+      <c r="I14" s="57" t="n"/>
+      <c r="J14" s="58" t="n"/>
+      <c r="K14" s="79" t="inlineStr"/>
+      <c r="L14" s="57" t="n"/>
+      <c r="M14" s="57" t="n"/>
+      <c r="N14" s="58" t="n"/>
+      <c r="O14" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="P14" s="57" t="n"/>
+      <c r="Q14" s="57" t="n"/>
+      <c r="R14" s="58" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>R8 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="n"/>
+      <c r="D15" s="57" t="n"/>
+      <c r="E15" s="57" t="n"/>
+      <c r="F15" s="57" t="n"/>
+      <c r="G15" s="57" t="n"/>
+      <c r="H15" s="57" t="n"/>
+      <c r="I15" s="57" t="n"/>
+      <c r="J15" s="58" t="n"/>
+      <c r="K15" s="81" t="inlineStr"/>
+      <c r="L15" s="57" t="n"/>
+      <c r="M15" s="57" t="n"/>
+      <c r="N15" s="58" t="n"/>
+      <c r="O15" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="P15" s="57" t="n"/>
+      <c r="Q15" s="57" t="n"/>
+      <c r="R15" s="58" t="n"/>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="C16" s="57" t="n"/>
+      <c r="D16" s="57" t="n"/>
+      <c r="E16" s="57" t="n"/>
+      <c r="F16" s="57" t="n"/>
+      <c r="G16" s="57" t="n"/>
+      <c r="H16" s="57" t="n"/>
+      <c r="I16" s="57" t="n"/>
+      <c r="J16" s="58" t="n"/>
+      <c r="K16" s="79" t="inlineStr"/>
+      <c r="L16" s="57" t="n"/>
+      <c r="M16" s="57" t="n"/>
+      <c r="N16" s="58" t="n"/>
+      <c r="O16" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: f08_a, f08_b, f08_c, f08_d, f08_e, f08_f, f08_g, f08_h</t>
+        </is>
+      </c>
+      <c r="P16" s="57" t="n"/>
+      <c r="Q16" s="57" t="n"/>
+      <c r="R16" s="58" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="A6:R6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>M09 – Opinions &amp; Views  |  Cross-Round Variable Tracker  (R1–R5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="55" t="inlineStr"/>
+      <c r="B2" s="55" t="inlineStr"/>
+      <c r="C2" s="55" t="inlineStr"/>
+      <c r="D2" s="56" t="inlineStr">
+        <is>
+          <t>R1
+Nov 2025</t>
+        </is>
+      </c>
+      <c r="E2" s="57" t="n"/>
+      <c r="F2" s="57" t="n"/>
+      <c r="G2" s="57" t="n"/>
+      <c r="H2" s="58" t="n"/>
+      <c r="I2" s="55" t="inlineStr"/>
+      <c r="J2" s="55" t="inlineStr"/>
+      <c r="K2" s="55" t="inlineStr"/>
+      <c r="L2" s="55" t="inlineStr"/>
+      <c r="M2" s="55" t="inlineStr"/>
+      <c r="N2" s="55" t="inlineStr"/>
+      <c r="O2" s="55" t="inlineStr"/>
+      <c r="P2" s="55" t="inlineStr"/>
+      <c r="Q2" s="55" t="inlineStr"/>
+      <c r="R2" s="55" t="inlineStr"/>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B3" s="59" t="inlineStr">
+        <is>
+          <t>Question Title</t>
+        </is>
+      </c>
+      <c r="C3" s="59" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D3" s="59" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E3" s="59" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F3" s="59" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="G3" s="59" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="H3" s="59" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="I3" s="59" t="inlineStr">
+        <is>
+          <t>Question Text (English)</t>
+        </is>
+      </c>
+      <c r="J3" s="59" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="K3" s="59" t="inlineStr">
+        <is>
+          <t># Codes R1</t>
+        </is>
+      </c>
+      <c r="L3" s="59" t="inlineStr">
+        <is>
+          <t># Codes R5</t>
+        </is>
+      </c>
+      <c r="M3" s="59" t="inlineStr">
+        <is>
+          <t>Title / Wording Change</t>
+        </is>
+      </c>
+      <c r="N3" s="59" t="inlineStr">
+        <is>
+          <t>Skip Logic Change</t>
+        </is>
+      </c>
+      <c r="O3" s="59" t="inlineStr">
+        <is>
+          <t>Skip Logic (R1)</t>
+        </is>
+      </c>
+      <c r="P3" s="59" t="inlineStr">
+        <is>
+          <t>Skip Logic (R5)</t>
+        </is>
+      </c>
+      <c r="Q3" s="59" t="inlineStr">
+        <is>
+          <t>Data Check Notes (R5)</t>
+        </is>
+      </c>
+      <c r="R3" s="59" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
           <t>V1</t>
         </is>
       </c>
@@ -7267,7 +7415,7 @@
       <c r="J19" s="58" t="n"/>
       <c r="K19" s="81" t="inlineStr">
         <is>
-          <t>log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, round, round, round, round, fmid_str</t>
+          <t>log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, round, round, round, round</t>
         </is>
       </c>
       <c r="L19" s="57" t="n"/>
@@ -7303,7 +7451,7 @@
       <c r="J20" s="58" t="n"/>
       <c r="K20" s="79" t="inlineStr">
         <is>
-          <t>log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, round, round, round, round, fmid_str</t>
+          <t>log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, round, round, round, round</t>
         </is>
       </c>
       <c r="L20" s="57" t="n"/>
@@ -7326,7 +7474,7 @@
       </c>
       <c r="B21" s="81" t="inlineStr">
         <is>
-          <t>v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v1, v5, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m</t>
+          <t>v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v1, v5, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, int_id, z8, call_status1, z17, z9, z18, z19, z20...</t>
         </is>
       </c>
       <c r="C21" s="57" t="n"/>
@@ -7339,7 +7487,7 @@
       <c r="J21" s="58" t="n"/>
       <c r="K21" s="81" t="inlineStr">
         <is>
-          <t>source_sheet, excess_int, excess_int, excess_int, excess_int, excess_int, emp_status, excess_int, round, excess_int, round, excess_int, excess_int, excess_int, fmid_str</t>
+          <t>source_sheet, log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, excess_int, excess_int, excess_int, excess_int, excess_int, emp_status, excess_int</t>
         </is>
       </c>
       <c r="L21" s="57" t="n"/>
@@ -7347,7 +7495,7 @@
       <c r="N21" s="58" t="n"/>
       <c r="O21" s="83" t="inlineStr">
         <is>
-          <t>Raw/derived only: v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m</t>
+          <t>Raw/derived only: call_status1, int_id, member_talkedto, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, x11, x12</t>
         </is>
       </c>
       <c r="P21" s="57" t="n"/>
@@ -7362,7 +7510,7 @@
       </c>
       <c r="B22" s="79" t="inlineStr">
         <is>
-          <t>v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v1, v5, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m</t>
+          <t>v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v1, v5, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, int_id, z8, call_status1, z17, z9, z18, z19, z20...</t>
         </is>
       </c>
       <c r="C22" s="57" t="n"/>
@@ -7375,7 +7523,7 @@
       <c r="J22" s="58" t="n"/>
       <c r="K22" s="79" t="inlineStr">
         <is>
-          <t>source_sheet, emp_status</t>
+          <t>source_sheet, log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, emp_status</t>
         </is>
       </c>
       <c r="L22" s="57" t="n"/>
@@ -7383,7 +7531,7 @@
       <c r="N22" s="58" t="n"/>
       <c r="O22" s="82" t="inlineStr">
         <is>
-          <t>Raw/derived only: v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m</t>
+          <t>Raw/derived only: call_status1, int_id, member_talkedto, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, x11, x12</t>
         </is>
       </c>
       <c r="P22" s="57" t="n"/>
@@ -7491,15 +7639,51 @@
       <c r="N25" s="58" t="n"/>
       <c r="O25" s="83" t="inlineStr">
         <is>
-          <t>Raw/derived only: call_status1, int_id, member_talkedto, v1, v13, v14, v15_a, v15_b, v15_c, v16, v17, v18, v5, v9_a, v9_c</t>
+          <t>Raw/derived only: call_status1, int_id, member_talkedto, v15_a, v15_b, v15_c, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l</t>
         </is>
       </c>
       <c r="P25" s="57" t="n"/>
       <c r="Q25" s="57" t="n"/>
       <c r="R25" s="58" t="n"/>
     </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B26" s="79" t="inlineStr">
+        <is>
+          <t>v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v1, v5, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l, v9_m, v13, v14, v15_a, v15_b, v15_c, v16, v17, v18...</t>
+        </is>
+      </c>
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="57" t="n"/>
+      <c r="F26" s="57" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n"/>
+      <c r="I26" s="57" t="n"/>
+      <c r="J26" s="58" t="n"/>
+      <c r="K26" s="79" t="inlineStr">
+        <is>
+          <t>source_sheet, log_round, int_name, status, refusal, completed, ongoing, no_contact, call_date, nd_count_more1, nd_count_less2, notsameday, comment_by_supervisor, emp_status</t>
+        </is>
+      </c>
+      <c r="L26" s="57" t="n"/>
+      <c r="M26" s="57" t="n"/>
+      <c r="N26" s="58" t="n"/>
+      <c r="O26" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: call_status1, int_id, member_talkedto, v15_a, v15_b, v15_c, v9_a, v9_c, v9_e, v9_f, v9_g, v9_i, v9_j, v9_k, v9_l</t>
+        </is>
+      </c>
+      <c r="P26" s="57" t="n"/>
+      <c r="Q26" s="57" t="n"/>
+      <c r="R26" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="K17:N17"/>
     <mergeCell ref="A16:R16"/>
@@ -7518,9 +7702,12 @@
     <mergeCell ref="O18:R18"/>
     <mergeCell ref="B24:J24"/>
     <mergeCell ref="B20:J20"/>
+    <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="K20:N20"/>
+    <mergeCell ref="B26:J26"/>
     <mergeCell ref="O20:R20"/>
+    <mergeCell ref="O26:R26"/>
     <mergeCell ref="B25:J25"/>
     <mergeCell ref="K22:N22"/>
     <mergeCell ref="O22:R22"/>
@@ -7541,7 +7728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7554,7 +7741,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -7563,7 +7750,9 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7633,50 +7822,60 @@
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
           <t>New in R2</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>New in R3</t>
         </is>
       </c>
-      <c r="M3" s="17" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t>New in R4</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="O3" s="17" t="inlineStr">
         <is>
           <t>New in R5</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t>New in R6</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="Q3" s="17" t="inlineStr">
         <is>
           <t>New in R7</t>
         </is>
       </c>
-      <c r="Q3" s="17" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
         <is>
           <t>New in R8</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="S3" s="17" t="inlineStr">
+        <is>
+          <t>New in R9</t>
+        </is>
+      </c>
+      <c r="T3" s="17" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
       </c>
-      <c r="S3" s="17" t="inlineStr">
+      <c r="U3" s="17" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="V3" s="17" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7718,7 +7917,7 @@
         <v>21</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L4" s="19" t="n">
         <v>0</v>
@@ -7730,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="19" t="n">
         <v>1</v>
-      </c>
-      <c r="P4" s="19" t="n">
-        <v>0</v>
       </c>
       <c r="Q4" s="19" t="n">
         <v>0</v>
@@ -7742,9 +7941,15 @@
         <v>0</v>
       </c>
       <c r="S4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="19" t="inlineStr"/>
+      <c r="V4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -7782,10 +7987,10 @@
         <v>19</v>
       </c>
       <c r="K5" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="M5" s="20" t="n">
         <v>0</v>
@@ -7806,9 +8011,15 @@
         <v>0</v>
       </c>
       <c r="S5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="T5" s="20" t="inlineStr"/>
+      <c r="V5" s="20" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -7843,10 +8054,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" s="19" t="n">
         <v>0</v>
@@ -7867,12 +8078,18 @@
         <v>0</v>
       </c>
       <c r="R6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="19" t="inlineStr"/>
+      <c r="T6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
@@ -7910,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="K7" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="M7" s="20" t="n">
         <v>10</v>
-      </c>
-      <c r="M7" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="N7" s="20" t="n">
         <v>0</v>
@@ -7934,9 +8151,15 @@
         <v>0</v>
       </c>
       <c r="S7" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" s="20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -7974,7 +8197,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L8" s="19" t="n">
         <v>0</v>
@@ -7998,9 +8221,15 @@
         <v>0</v>
       </c>
       <c r="S8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="T8" s="19" t="inlineStr"/>
+      <c r="V8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
@@ -8038,13 +8267,13 @@
         <v>15</v>
       </c>
       <c r="K9" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="M9" s="20" t="n">
         <v>10</v>
-      </c>
-      <c r="M9" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="N9" s="20" t="n">
         <v>0</v>
@@ -8062,9 +8291,15 @@
         <v>0</v>
       </c>
       <c r="S9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="T9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -8102,7 +8337,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L10" s="19" t="n">
         <v>0</v>
@@ -8111,10 +8346,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="19" t="n">
         <v>2</v>
-      </c>
-      <c r="O10" s="19" t="n">
-        <v>0</v>
       </c>
       <c r="P10" s="19" t="n">
         <v>0</v>
@@ -8126,9 +8361,15 @@
         <v>0</v>
       </c>
       <c r="S10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="T10" s="19" t="inlineStr"/>
+      <c r="V10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -8166,7 +8407,7 @@
         <v>16</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L11" s="20" t="n">
         <v>0</v>
@@ -8175,10 +8416,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20" t="n">
         <v>13</v>
-      </c>
-      <c r="O11" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="P11" s="20" t="n">
         <v>0</v>
@@ -8190,9 +8431,15 @@
         <v>0</v>
       </c>
       <c r="S11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8230,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="19" t="n">
         <v>0</v>
@@ -8256,7 +8503,13 @@
       <c r="S12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="19" t="inlineStr"/>
+      <c r="T12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
@@ -8294,7 +8547,7 @@
         <v>9</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L13" s="20" t="n">
         <v>0</v>
@@ -8306,21 +8559,27 @@
         <v>0</v>
       </c>
       <c r="O13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="20" t="n">
         <v>6</v>
-      </c>
-      <c r="P13" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="S13" s="20" t="n">
+      <c r="U13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="20" t="inlineStr"/>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8337,7 +8596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11144,7 +11403,7 @@
       </c>
       <c r="F80" s="42" t="inlineStr">
         <is>
-          <t>NUMBER OF DAYS - DISRUPTION IN WATER SUPPLY</t>
+          <t>NUMBER OF DAYS - DISRUPTION IN DRINKING WATER SUPPLY</t>
         </is>
       </c>
       <c r="G80" s="42" t="inlineStr"/>
@@ -16723,6 +16982,234 @@
           <t>Code 1: Go to V16; Code 2: Go to V15; Code 3: Go to V15; Code 4: Go to V15; Code 98: Go to V16; Code 99: Go to V16</t>
         </is>
       </c>
+    </row>
+    <row r="230" ht="35" customHeight="1">
+      <c r="A230" s="33" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B230" s="34" t="inlineStr">
+        <is>
+          <t>M02 – Education</t>
+        </is>
+      </c>
+      <c r="C230" s="35" t="inlineStr">
+        <is>
+          <t>ED17</t>
+        </is>
+      </c>
+      <c r="D230" s="36" t="inlineStr">
+        <is>
+          <t>New Question</t>
+        </is>
+      </c>
+      <c r="E230" s="37" t="inlineStr">
+        <is>
+          <t>First appears in R8</t>
+        </is>
+      </c>
+      <c r="F230" s="37" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF ENROLLING IN AY 2026-2027</t>
+        </is>
+      </c>
+      <c r="G230" s="37" t="inlineStr">
+        <is>
+          <t>Has [NAME] enrolled in the academic year 2026-2027?</t>
+        </is>
+      </c>
+      <c r="H230" s="37" t="inlineStr"/>
+    </row>
+    <row r="231" ht="35" customHeight="1">
+      <c r="A231" s="33" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B231" s="34" t="inlineStr">
+        <is>
+          <t>M02 – Education</t>
+        </is>
+      </c>
+      <c r="C231" s="35" t="inlineStr">
+        <is>
+          <t>ED2</t>
+        </is>
+      </c>
+      <c r="D231" s="36" t="inlineStr">
+        <is>
+          <t>New Question</t>
+        </is>
+      </c>
+      <c r="E231" s="37" t="inlineStr">
+        <is>
+          <t>First appears in R8</t>
+        </is>
+      </c>
+      <c r="F231" s="37" t="inlineStr">
+        <is>
+          <t>TYPE OF SCHOOL/INSTITUTION</t>
+        </is>
+      </c>
+      <c r="G231" s="37" t="inlineStr">
+        <is>
+          <t>Is the school/insitution of [NAME] public, private, or home-schooled?</t>
+        </is>
+      </c>
+      <c r="H231" s="37" t="inlineStr"/>
+    </row>
+    <row r="232" ht="35" customHeight="1">
+      <c r="A232" s="33" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B232" s="34" t="inlineStr">
+        <is>
+          <t>M02 – Education</t>
+        </is>
+      </c>
+      <c r="C232" s="35" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="D232" s="36" t="inlineStr">
+        <is>
+          <t>New Question</t>
+        </is>
+      </c>
+      <c r="E232" s="37" t="inlineStr">
+        <is>
+          <t>First appears in R8</t>
+        </is>
+      </c>
+      <c r="F232" s="37" t="inlineStr">
+        <is>
+          <t>UPCOMING GRADE LEVEL</t>
+        </is>
+      </c>
+      <c r="G232" s="37" t="inlineStr">
+        <is>
+          <t>In what grade was/will be &lt;NAME&gt; enrolled? In which level?</t>
+        </is>
+      </c>
+      <c r="H232" s="37" t="inlineStr"/>
+    </row>
+    <row r="233" ht="35" customHeight="1">
+      <c r="A233" s="33" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B233" s="34" t="inlineStr">
+        <is>
+          <t>M02 – Education</t>
+        </is>
+      </c>
+      <c r="C233" s="35" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="D233" s="36" t="inlineStr">
+        <is>
+          <t>New Question</t>
+        </is>
+      </c>
+      <c r="E233" s="37" t="inlineStr">
+        <is>
+          <t>First appears in R8</t>
+        </is>
+      </c>
+      <c r="F233" s="37" t="inlineStr">
+        <is>
+          <t>AMOUNT SPENT ON EDUCATION IN CURRENT AY 2026-2027</t>
+        </is>
+      </c>
+      <c r="G233" s="37" t="inlineStr">
+        <is>
+          <t>How much did your household spend on [NAME's] education for this academic year (2026-2027) on...?</t>
+        </is>
+      </c>
+      <c r="H233" s="37" t="inlineStr"/>
+    </row>
+    <row r="234" ht="35" customHeight="1">
+      <c r="A234" s="33" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B234" s="34" t="inlineStr">
+        <is>
+          <t>M02 – Education</t>
+        </is>
+      </c>
+      <c r="C234" s="35" t="inlineStr">
+        <is>
+          <t>ED20</t>
+        </is>
+      </c>
+      <c r="D234" s="36" t="inlineStr">
+        <is>
+          <t>New Question</t>
+        </is>
+      </c>
+      <c r="E234" s="37" t="inlineStr">
+        <is>
+          <t>First appears in R8</t>
+        </is>
+      </c>
+      <c r="F234" s="37" t="inlineStr">
+        <is>
+          <t>REASONS FOR NOT CURRENTLY ENROLLING</t>
+        </is>
+      </c>
+      <c r="G234" s="37" t="inlineStr">
+        <is>
+          <t>Why is [HH MEMBER] not attending school this academic year 2026-2027?</t>
+        </is>
+      </c>
+      <c r="H234" s="37" t="inlineStr"/>
+    </row>
+    <row r="235" ht="35" customHeight="1">
+      <c r="A235" s="23" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B235" s="24" t="inlineStr">
+        <is>
+          <t>M03 – Shocks</t>
+        </is>
+      </c>
+      <c r="C235" s="25" t="inlineStr">
+        <is>
+          <t>SH4</t>
+        </is>
+      </c>
+      <c r="D235" s="26" t="inlineStr">
+        <is>
+          <t>Title/Wording Change</t>
+        </is>
+      </c>
+      <c r="E235" s="27" t="inlineStr">
+        <is>
+          <t>R7→R8: 'NUMBER OF DAYS - DISRUPTION IN WATER SUPPLY' → 'NUMBER OF DAYS - DISRUPTION IN DRINKING WATER SUPPLY'</t>
+        </is>
+      </c>
+      <c r="F235" s="27" t="inlineStr">
+        <is>
+          <t>NUMBER OF DAYS - DISRUPTION IN DRINKING WATER SUPPLY</t>
+        </is>
+      </c>
+      <c r="G235" s="27" t="inlineStr">
+        <is>
+          <t>On how many days was there a disruption in your drinking water supply at home over the PAST 30 DAYS?</t>
+        </is>
+      </c>
+      <c r="H235" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -17675,7 +18162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19452,8 +19939,36 @@
       <c r="Q35" s="57" t="n"/>
       <c r="R35" s="58" t="n"/>
     </row>
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B36" s="79" t="inlineStr"/>
+      <c r="C36" s="57" t="n"/>
+      <c r="D36" s="57" t="n"/>
+      <c r="E36" s="57" t="n"/>
+      <c r="F36" s="57" t="n"/>
+      <c r="G36" s="57" t="n"/>
+      <c r="H36" s="57" t="n"/>
+      <c r="I36" s="57" t="n"/>
+      <c r="J36" s="58" t="n"/>
+      <c r="K36" s="79" t="inlineStr"/>
+      <c r="L36" s="57" t="n"/>
+      <c r="M36" s="57" t="n"/>
+      <c r="N36" s="58" t="n"/>
+      <c r="O36" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P36" s="57" t="n"/>
+      <c r="Q36" s="57" t="n"/>
+      <c r="R36" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="A26:R26"/>
@@ -19469,10 +19984,13 @@
     <mergeCell ref="B30:J30"/>
     <mergeCell ref="O33:R33"/>
     <mergeCell ref="B33:J33"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="O36:R36"/>
     <mergeCell ref="O30:R30"/>
     <mergeCell ref="K29:N29"/>
     <mergeCell ref="B32:J32"/>
     <mergeCell ref="K35:N35"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="O29:R29"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="K32:N32"/>
@@ -19495,7 +20013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21226,22 +21744,61 @@
       <c r="N33" s="58" t="n"/>
       <c r="O33" s="83" t="inlineStr">
         <is>
-          <t>Raw/derived only: age, d25, d28, d31, d32, d33, d6, fmida1, fmida10, fmida11, fmida2, fmida24, fmida27, fmida5, fmida6</t>
+          <t>Raw/derived only: age, fmida1, fmida10, fmida11, fmida2, fmida24, fmida27, fmida5, fmida6, fmida8, fmida9, gender, h17, ia2, ia3_a</t>
         </is>
       </c>
       <c r="P33" s="57" t="n"/>
       <c r="Q33" s="57" t="n"/>
       <c r="R33" s="58" t="n"/>
     </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B34" s="79" t="inlineStr">
+        <is>
+          <t>isfmid, d25, d28, d33, age, gender, d31, d32, d6, isfmid, fmida1, fmida2, fmida5, fmida6, fmida8, fmida9, fmida10, fmida11, fmida24, fmida27, income_fmida1, income_fmida24, income_fmida27, ia2, ia3_a, ia3_b, ia3_c, ia3_d, ia3_e, ia3_f...</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="n"/>
+      <c r="D34" s="57" t="n"/>
+      <c r="E34" s="57" t="n"/>
+      <c r="F34" s="57" t="n"/>
+      <c r="G34" s="57" t="n"/>
+      <c r="H34" s="57" t="n"/>
+      <c r="I34" s="57" t="n"/>
+      <c r="J34" s="58" t="n"/>
+      <c r="K34" s="79" t="inlineStr">
+        <is>
+          <t>hhsize, child_check, round, round</t>
+        </is>
+      </c>
+      <c r="L34" s="57" t="n"/>
+      <c r="M34" s="57" t="n"/>
+      <c r="N34" s="58" t="n"/>
+      <c r="O34" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: age, fmida1, fmida10, fmida11, fmida2, fmida24, fmida27, fmida5, fmida6, fmida8, fmida9, gender, ia2, ia3_a, ia3_b</t>
+        </is>
+      </c>
+      <c r="P34" s="57" t="n"/>
+      <c r="Q34" s="57" t="n"/>
+      <c r="R34" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="K28:N28"/>
+    <mergeCell ref="B34:J34"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K34:N34"/>
     <mergeCell ref="K30:N30"/>
+    <mergeCell ref="O34:R34"/>
     <mergeCell ref="O28:R28"/>
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="B30:J30"/>
@@ -21276,7 +21833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21581,182 +22138,326 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="76" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>ED17</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>INCIDENCE OF ENROLLING IN AY 2026-2027</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="inlineStr">
+        <is>
+          <t>New in R8</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>Has [NAME] enrolled in the academic year 2026-2027?</t>
+        </is>
+      </c>
+      <c r="J6" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr"/>
+      <c r="M6" s="37" t="inlineStr"/>
+      <c r="N6" s="72" t="inlineStr">
+        <is>
+          <t>Added in R8</t>
+        </is>
+      </c>
+      <c r="O6" s="37" t="inlineStr"/>
+      <c r="P6" s="37" t="inlineStr"/>
+      <c r="Q6" s="37" t="inlineStr"/>
+      <c r="R6" s="37" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>ED2</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>TYPE OF SCHOOL/INSTITUTION</t>
+        </is>
+      </c>
+      <c r="C7" s="74" t="inlineStr">
+        <is>
+          <t>New in R8</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>Is the school/insitution of [NAME] public, private, or home-schooled?</t>
+        </is>
+      </c>
+      <c r="J7" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr"/>
+      <c r="L7" s="33" t="inlineStr"/>
+      <c r="M7" s="37" t="inlineStr"/>
+      <c r="N7" s="72" t="inlineStr">
+        <is>
+          <t>Added in R8</t>
+        </is>
+      </c>
+      <c r="O7" s="37" t="inlineStr"/>
+      <c r="P7" s="37" t="inlineStr"/>
+      <c r="Q7" s="37" t="inlineStr"/>
+      <c r="R7" s="37" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>UPCOMING GRADE LEVEL</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="inlineStr">
+        <is>
+          <t>New in R8</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="37" t="inlineStr">
+        <is>
+          <t>In what grade was/will be &lt;NAME&gt; enrolled? In which level?</t>
+        </is>
+      </c>
+      <c r="J8" s="37" t="inlineStr"/>
+      <c r="K8" s="33" t="inlineStr"/>
+      <c r="L8" s="33" t="inlineStr"/>
+      <c r="M8" s="37" t="inlineStr"/>
+      <c r="N8" s="37" t="inlineStr"/>
+      <c r="O8" s="37" t="inlineStr"/>
+      <c r="P8" s="37" t="inlineStr"/>
+      <c r="Q8" s="37" t="inlineStr"/>
+      <c r="R8" s="37" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>AMOUNT SPENT ON EDUCATION IN CURRENT AY 2026-2027</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>New in R8</t>
+        </is>
+      </c>
+      <c r="D9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="37" t="inlineStr">
+        <is>
+          <t>How much did your household spend on [NAME's] education for this academic year (2026-2027) on...?</t>
+        </is>
+      </c>
+      <c r="J9" s="37" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr"/>
+      <c r="L9" s="33" t="inlineStr"/>
+      <c r="M9" s="37" t="inlineStr"/>
+      <c r="N9" s="37" t="inlineStr"/>
+      <c r="O9" s="37" t="inlineStr"/>
+      <c r="P9" s="37" t="inlineStr"/>
+      <c r="Q9" s="37" t="inlineStr"/>
+      <c r="R9" s="37" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>ED20</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>REASONS FOR NOT CURRENTLY ENROLLING</t>
+        </is>
+      </c>
+      <c r="C10" s="74" t="inlineStr">
+        <is>
+          <t>New in R8</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Why is [HH MEMBER] not attending school this academic year 2026-2027?</t>
+        </is>
+      </c>
+      <c r="J10" s="37" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr"/>
+      <c r="L10" s="33" t="inlineStr"/>
+      <c r="M10" s="37" t="inlineStr"/>
+      <c r="N10" s="37" t="inlineStr"/>
+      <c r="O10" s="37" t="inlineStr"/>
+      <c r="P10" s="37" t="inlineStr"/>
+      <c r="Q10" s="37" t="inlineStr"/>
+      <c r="R10" s="37" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>DO-FILE VARIABLE DETAILS (destring/generate operations per round)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>Variables processed (destring/tostring)</t>
-        </is>
-      </c>
-      <c r="C8" s="57" t="n"/>
-      <c r="D8" s="57" t="n"/>
-      <c r="E8" s="57" t="n"/>
-      <c r="F8" s="57" t="n"/>
-      <c r="G8" s="57" t="n"/>
-      <c r="H8" s="57" t="n"/>
-      <c r="I8" s="57" t="n"/>
-      <c r="J8" s="58" t="n"/>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="78" t="inlineStr">
-        <is>
-          <t>R1 (Nov 2025)</t>
-        </is>
-      </c>
-      <c r="B9" s="79" t="inlineStr">
-        <is>
-          <t>ed15, ed16</t>
-        </is>
-      </c>
-      <c r="C9" s="57" t="n"/>
-      <c r="D9" s="57" t="n"/>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="57" t="n"/>
-      <c r="H9" s="57" t="n"/>
-      <c r="I9" s="57" t="n"/>
-      <c r="J9" s="58" t="n"/>
-      <c r="K9" s="79" t="inlineStr"/>
-      <c r="L9" s="57" t="n"/>
-      <c r="M9" s="57" t="n"/>
-      <c r="N9" s="58" t="n"/>
-      <c r="O9" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
-        </is>
-      </c>
-      <c r="P9" s="57" t="n"/>
-      <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="58" t="n"/>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="80" t="inlineStr">
-        <is>
-          <t>R2 (Dec 2025)</t>
-        </is>
-      </c>
-      <c r="B10" s="81" t="inlineStr">
-        <is>
-          <t>ed15, ed16</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="57" t="n"/>
-      <c r="H10" s="57" t="n"/>
-      <c r="I10" s="57" t="n"/>
-      <c r="J10" s="58" t="n"/>
-      <c r="K10" s="81" t="inlineStr">
-        <is>
-          <t>fmid_str</t>
-        </is>
-      </c>
-      <c r="L10" s="57" t="n"/>
-      <c r="M10" s="57" t="n"/>
-      <c r="N10" s="58" t="n"/>
-      <c r="O10" s="81" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
-        </is>
-      </c>
-      <c r="P10" s="57" t="n"/>
-      <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="58" t="n"/>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="78" t="inlineStr">
-        <is>
-          <t>R3 (Jan 2026)</t>
-        </is>
-      </c>
-      <c r="B11" s="79" t="inlineStr">
-        <is>
-          <t>ed15, ed16, ed15, ed16</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-      <c r="I11" s="57" t="n"/>
-      <c r="J11" s="58" t="n"/>
-      <c r="K11" s="79" t="inlineStr">
-        <is>
-          <t>fmid</t>
-        </is>
-      </c>
-      <c r="L11" s="57" t="n"/>
-      <c r="M11" s="57" t="n"/>
-      <c r="N11" s="58" t="n"/>
-      <c r="O11" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
-        </is>
-      </c>
-      <c r="P11" s="57" t="n"/>
-      <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="58" t="n"/>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="80" t="inlineStr">
-        <is>
-          <t>R4 (Feb 2026)</t>
-        </is>
-      </c>
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>ed15, ed15</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="57" t="n"/>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="57" t="n"/>
-      <c r="H12" s="57" t="n"/>
-      <c r="I12" s="57" t="n"/>
-      <c r="J12" s="58" t="n"/>
-      <c r="K12" s="81" t="inlineStr">
-        <is>
-          <t>round, fmid</t>
-        </is>
-      </c>
-      <c r="L12" s="57" t="n"/>
-      <c r="M12" s="57" t="n"/>
-      <c r="N12" s="58" t="n"/>
-      <c r="O12" s="81" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
-        </is>
-      </c>
-      <c r="P12" s="57" t="n"/>
-      <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="58" t="n"/>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="78" t="inlineStr">
-        <is>
-          <t>R5 (Mar 2026)</t>
-        </is>
-      </c>
-      <c r="B13" s="79" t="inlineStr">
-        <is>
-          <t>ed15, ed15</t>
         </is>
       </c>
       <c r="C13" s="57" t="n"/>
@@ -21767,32 +22468,16 @@
       <c r="H13" s="57" t="n"/>
       <c r="I13" s="57" t="n"/>
       <c r="J13" s="58" t="n"/>
-      <c r="K13" s="79" t="inlineStr">
-        <is>
-          <t>round, round, fmid</t>
-        </is>
-      </c>
-      <c r="L13" s="57" t="n"/>
-      <c r="M13" s="57" t="n"/>
-      <c r="N13" s="58" t="n"/>
-      <c r="O13" s="79" t="inlineStr">
-        <is>
-          <t>Matches questionnaire</t>
-        </is>
-      </c>
-      <c r="P13" s="57" t="n"/>
-      <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="58" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="80" t="inlineStr">
-        <is>
-          <t>R6 (Apr 2026)</t>
-        </is>
-      </c>
-      <c r="B14" s="81" t="inlineStr">
-        <is>
-          <t>ed15, ed15</t>
+      <c r="A14" s="78" t="inlineStr">
+        <is>
+          <t>R1 (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>ed15, ed16</t>
         </is>
       </c>
       <c r="C14" s="57" t="n"/>
@@ -21803,15 +22488,11 @@
       <c r="H14" s="57" t="n"/>
       <c r="I14" s="57" t="n"/>
       <c r="J14" s="58" t="n"/>
-      <c r="K14" s="81" t="inlineStr">
-        <is>
-          <t>round, round, fmid</t>
-        </is>
-      </c>
+      <c r="K14" s="79" t="inlineStr"/>
       <c r="L14" s="57" t="n"/>
       <c r="M14" s="57" t="n"/>
       <c r="N14" s="58" t="n"/>
-      <c r="O14" s="81" t="inlineStr">
+      <c r="O14" s="79" t="inlineStr">
         <is>
           <t>Matches questionnaire</t>
         </is>
@@ -21821,14 +22502,14 @@
       <c r="R14" s="58" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="78" t="inlineStr">
-        <is>
-          <t>R7 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B15" s="79" t="inlineStr">
-        <is>
-          <t>ed15, ed15</t>
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>R2 (Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>ed15, ed16</t>
         </is>
       </c>
       <c r="C15" s="57" t="n"/>
@@ -21839,15 +22520,15 @@
       <c r="H15" s="57" t="n"/>
       <c r="I15" s="57" t="n"/>
       <c r="J15" s="58" t="n"/>
-      <c r="K15" s="79" t="inlineStr">
-        <is>
-          <t>round, round, fmid</t>
+      <c r="K15" s="81" t="inlineStr">
+        <is>
+          <t>fmid_str</t>
         </is>
       </c>
       <c r="L15" s="57" t="n"/>
       <c r="M15" s="57" t="n"/>
       <c r="N15" s="58" t="n"/>
-      <c r="O15" s="79" t="inlineStr">
+      <c r="O15" s="81" t="inlineStr">
         <is>
           <t>Matches questionnaire</t>
         </is>
@@ -21857,14 +22538,14 @@
       <c r="R15" s="58" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="80" t="inlineStr">
-        <is>
-          <t>R8 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B16" s="81" t="inlineStr">
-        <is>
-          <t>ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i, ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i</t>
+      <c r="A16" s="78" t="inlineStr">
+        <is>
+          <t>R3 (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>ed15, ed16, ed15, ed16</t>
         </is>
       </c>
       <c r="C16" s="57" t="n"/>
@@ -21875,55 +22556,274 @@
       <c r="H16" s="57" t="n"/>
       <c r="I16" s="57" t="n"/>
       <c r="J16" s="58" t="n"/>
-      <c r="K16" s="81" t="inlineStr">
-        <is>
-          <t>round, round, fmid</t>
+      <c r="K16" s="79" t="inlineStr">
+        <is>
+          <t>fmid</t>
         </is>
       </c>
       <c r="L16" s="57" t="n"/>
       <c r="M16" s="57" t="n"/>
       <c r="N16" s="58" t="n"/>
-      <c r="O16" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: ed15, ed17, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i, ed2</t>
+      <c r="O16" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
         </is>
       </c>
       <c r="P16" s="57" t="n"/>
       <c r="Q16" s="57" t="n"/>
       <c r="R16" s="58" t="n"/>
     </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>R4 (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>ed15, ed15</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="n"/>
+      <c r="D17" s="57" t="n"/>
+      <c r="E17" s="57" t="n"/>
+      <c r="F17" s="57" t="n"/>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="57" t="n"/>
+      <c r="I17" s="57" t="n"/>
+      <c r="J17" s="58" t="n"/>
+      <c r="K17" s="81" t="inlineStr">
+        <is>
+          <t>round, fmid</t>
+        </is>
+      </c>
+      <c r="L17" s="57" t="n"/>
+      <c r="M17" s="57" t="n"/>
+      <c r="N17" s="58" t="n"/>
+      <c r="O17" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P17" s="57" t="n"/>
+      <c r="Q17" s="57" t="n"/>
+      <c r="R17" s="58" t="n"/>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="78" t="inlineStr">
+        <is>
+          <t>R5 (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>ed15, ed15</t>
+        </is>
+      </c>
+      <c r="C18" s="57" t="n"/>
+      <c r="D18" s="57" t="n"/>
+      <c r="E18" s="57" t="n"/>
+      <c r="F18" s="57" t="n"/>
+      <c r="G18" s="57" t="n"/>
+      <c r="H18" s="57" t="n"/>
+      <c r="I18" s="57" t="n"/>
+      <c r="J18" s="58" t="n"/>
+      <c r="K18" s="79" t="inlineStr">
+        <is>
+          <t>round, round, fmid</t>
+        </is>
+      </c>
+      <c r="L18" s="57" t="n"/>
+      <c r="M18" s="57" t="n"/>
+      <c r="N18" s="58" t="n"/>
+      <c r="O18" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P18" s="57" t="n"/>
+      <c r="Q18" s="57" t="n"/>
+      <c r="R18" s="58" t="n"/>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>R6 (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>ed15, ed15</t>
+        </is>
+      </c>
+      <c r="C19" s="57" t="n"/>
+      <c r="D19" s="57" t="n"/>
+      <c r="E19" s="57" t="n"/>
+      <c r="F19" s="57" t="n"/>
+      <c r="G19" s="57" t="n"/>
+      <c r="H19" s="57" t="n"/>
+      <c r="I19" s="57" t="n"/>
+      <c r="J19" s="58" t="n"/>
+      <c r="K19" s="81" t="inlineStr">
+        <is>
+          <t>round, round, fmid</t>
+        </is>
+      </c>
+      <c r="L19" s="57" t="n"/>
+      <c r="M19" s="57" t="n"/>
+      <c r="N19" s="58" t="n"/>
+      <c r="O19" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P19" s="57" t="n"/>
+      <c r="Q19" s="57" t="n"/>
+      <c r="R19" s="58" t="n"/>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="78" t="inlineStr">
+        <is>
+          <t>R7 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>ed15, ed15</t>
+        </is>
+      </c>
+      <c r="C20" s="57" t="n"/>
+      <c r="D20" s="57" t="n"/>
+      <c r="E20" s="57" t="n"/>
+      <c r="F20" s="57" t="n"/>
+      <c r="G20" s="57" t="n"/>
+      <c r="H20" s="57" t="n"/>
+      <c r="I20" s="57" t="n"/>
+      <c r="J20" s="58" t="n"/>
+      <c r="K20" s="79" t="inlineStr">
+        <is>
+          <t>round, round, fmid</t>
+        </is>
+      </c>
+      <c r="L20" s="57" t="n"/>
+      <c r="M20" s="57" t="n"/>
+      <c r="N20" s="58" t="n"/>
+      <c r="O20" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P20" s="57" t="n"/>
+      <c r="Q20" s="57" t="n"/>
+      <c r="R20" s="58" t="n"/>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>R8 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i, ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="57" t="n"/>
+      <c r="F21" s="57" t="n"/>
+      <c r="G21" s="57" t="n"/>
+      <c r="H21" s="57" t="n"/>
+      <c r="I21" s="57" t="n"/>
+      <c r="J21" s="58" t="n"/>
+      <c r="K21" s="81" t="inlineStr">
+        <is>
+          <t>round, round, fmid</t>
+        </is>
+      </c>
+      <c r="L21" s="57" t="n"/>
+      <c r="M21" s="57" t="n"/>
+      <c r="N21" s="58" t="n"/>
+      <c r="O21" s="83" t="inlineStr">
+        <is>
+          <t>Raw/derived only: ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i</t>
+        </is>
+      </c>
+      <c r="P21" s="57" t="n"/>
+      <c r="Q21" s="57" t="n"/>
+      <c r="R21" s="58" t="n"/>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i, ed15, ed17, ed2, ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i</t>
+        </is>
+      </c>
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="57" t="n"/>
+      <c r="E22" s="57" t="n"/>
+      <c r="F22" s="57" t="n"/>
+      <c r="G22" s="57" t="n"/>
+      <c r="H22" s="57" t="n"/>
+      <c r="I22" s="57" t="n"/>
+      <c r="J22" s="58" t="n"/>
+      <c r="K22" s="79" t="inlineStr">
+        <is>
+          <t>round, round, fmid</t>
+        </is>
+      </c>
+      <c r="L22" s="57" t="n"/>
+      <c r="M22" s="57" t="n"/>
+      <c r="N22" s="58" t="n"/>
+      <c r="O22" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: ed18, ed19_a, ed19_b, ed19_c, ed19_d, ed19_e, ed19_f, ed19_g, ed19_h, ed19_i</t>
+        </is>
+      </c>
+      <c r="P22" s="57" t="n"/>
+      <c r="Q22" s="57" t="n"/>
+      <c r="R22" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B11:J11"/>
+  <mergeCells count="33">
     <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A7:R7"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="K17:N17"/>
     <mergeCell ref="B14:J14"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="B17:J17"/>
     <mergeCell ref="B13:J13"/>
     <mergeCell ref="O14:R14"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="A12:R12"/>
     <mergeCell ref="K13:N13"/>
-    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="K18:N18"/>
     <mergeCell ref="O13:R13"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B9:J9"/>
     <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O19:R19"/>
     <mergeCell ref="K15:N15"/>
-    <mergeCell ref="K9:N9"/>
     <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O18:R18"/>
     <mergeCell ref="B15:J15"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:R20"/>
     <mergeCell ref="B16:J16"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="B22:J22"/>
     <mergeCell ref="O16:R16"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="O21:R21"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21935,7 +22835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22387,14 +23287,14 @@
       <c r="R7" s="27" t="inlineStr"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>SH4</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>NUMBER OF DAYS - DISRUPTION IN WATER SUPPLY</t>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>NUMBER OF DAYS - DISRUPTION IN DRINKING WATER SUPPLY</t>
         </is>
       </c>
       <c r="C8" s="62" t="inlineStr">
@@ -22427,29 +23327,33 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I8" s="64" t="inlineStr">
-        <is>
-          <t>On how many days was there a disruption in your water supply at home over the PAST 30 DAYS?</t>
-        </is>
-      </c>
-      <c r="J8" s="64" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t>On how many days was there a disruption in your drinking water supply at home over the PAST 30 DAYS?</t>
+        </is>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>Numeric</t>
         </is>
       </c>
-      <c r="K8" s="65" t="inlineStr"/>
-      <c r="L8" s="65" t="inlineStr"/>
-      <c r="M8" s="64" t="inlineStr"/>
-      <c r="N8" s="64" t="inlineStr"/>
-      <c r="O8" s="64" t="inlineStr"/>
-      <c r="P8" s="64" t="inlineStr"/>
+      <c r="K8" s="23" t="inlineStr"/>
+      <c r="L8" s="23" t="inlineStr"/>
+      <c r="M8" s="72" t="inlineStr">
+        <is>
+          <t>R7→R8: 'NUMBER OF DAYS - DISRUPTION IN WATER SUPPLY' → 'NUMBER OF DAYS - DISRUPTION IN DRINKING WATER SUPPLY'</t>
+        </is>
+      </c>
+      <c r="N8" s="27" t="inlineStr"/>
+      <c r="O8" s="27" t="inlineStr"/>
+      <c r="P8" s="27" t="inlineStr"/>
       <c r="Q8" s="70" t="inlineStr">
         <is>
           <t>Answers must be in days
 Valid answer: 01-30</t>
         </is>
       </c>
-      <c r="R8" s="64" t="inlineStr"/>
+      <c r="R8" s="27" t="inlineStr"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="66" t="inlineStr">
@@ -23225,7 +24129,7 @@
       <c r="Q19" s="37" t="inlineStr"/>
       <c r="R19" s="37" t="inlineStr">
         <is>
-          <t>Added reference to R3</t>
+          <t>Revised reference to R6 (latest data)</t>
         </is>
       </c>
     </row>
@@ -23711,24 +24615,63 @@
       <c r="L33" s="57" t="n"/>
       <c r="M33" s="57" t="n"/>
       <c r="N33" s="58" t="n"/>
-      <c r="O33" s="83" t="inlineStr">
-        <is>
-          <t>Raw/derived only: el5, n5, sh1, sh3, sh4</t>
+      <c r="O33" s="81" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
         </is>
       </c>
       <c r="P33" s="57" t="n"/>
       <c r="Q33" s="57" t="n"/>
       <c r="R33" s="58" t="n"/>
     </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B34" s="79" t="inlineStr">
+        <is>
+          <t>sh1, sh3, sh4, el5, n5, nh14, nh15</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="n"/>
+      <c r="D34" s="57" t="n"/>
+      <c r="E34" s="57" t="n"/>
+      <c r="F34" s="57" t="n"/>
+      <c r="G34" s="57" t="n"/>
+      <c r="H34" s="57" t="n"/>
+      <c r="I34" s="57" t="n"/>
+      <c r="J34" s="58" t="n"/>
+      <c r="K34" s="79" t="inlineStr">
+        <is>
+          <t>shock_index_str</t>
+        </is>
+      </c>
+      <c r="L34" s="57" t="n"/>
+      <c r="M34" s="57" t="n"/>
+      <c r="N34" s="58" t="n"/>
+      <c r="O34" s="79" t="inlineStr">
+        <is>
+          <t>Matches questionnaire</t>
+        </is>
+      </c>
+      <c r="P34" s="57" t="n"/>
+      <c r="Q34" s="57" t="n"/>
+      <c r="R34" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="K28:N28"/>
+    <mergeCell ref="B34:J34"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K34:N34"/>
     <mergeCell ref="K30:N30"/>
+    <mergeCell ref="O34:R34"/>
     <mergeCell ref="O28:R28"/>
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="B30:J30"/>
@@ -23763,7 +24706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25570,7 +26513,7 @@
       <c r="J30" s="58" t="n"/>
       <c r="K30" s="79" t="inlineStr">
         <is>
-          <t>a19_11, a19_12, a19_13, a19_14, a19_15, a19_16, a19_17, a21_31, a21_32, a21_33, a21_34, a21_35, a21_36, a21_37, a21_97, a19_11, a19_12, a19_13, a19_14, a19_15</t>
+          <t>a19_11, a19_12, a19_13, a19_15, a19_17, a19_18, a19_19, a21_43, a21_44, a21_45, a21_49, a21_50, a21_51, a21_52, a21_97, a19_11, a19_12, a19_13, a19_15, a19_17</t>
         </is>
       </c>
       <c r="L30" s="57" t="n"/>
@@ -25826,15 +26769,54 @@
       <c r="N37" s="58" t="n"/>
       <c r="O37" s="83" t="inlineStr">
         <is>
-          <t>Raw/derived only: a1, a10, a11, a16, a17, a18, a20, a22, a23, a24, a25_olda10, a25_olda11, a25_olda6, a25_olda8a9, a26</t>
+          <t>Raw/derived only: a25_olda10, a25_olda11, a25_olda6, a25_olda8a9</t>
         </is>
       </c>
       <c r="P37" s="57" t="n"/>
       <c r="Q37" s="57" t="n"/>
       <c r="R37" s="58" t="n"/>
     </row>
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="78" t="inlineStr">
+        <is>
+          <t>R9 (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="B38" s="79" t="inlineStr">
+        <is>
+          <t>a24, a27, a25_olda6, a25_olda8a9, a25_olda10, a25_olda11, a1, a26, a3, a5, a6, a7, a8, a9, a10, a11, a16, a17, a18, a20, a22, a23, a1, a26, a3, a5, a6, a7, a8, a9...</t>
+        </is>
+      </c>
+      <c r="C38" s="57" t="n"/>
+      <c r="D38" s="57" t="n"/>
+      <c r="E38" s="57" t="n"/>
+      <c r="F38" s="57" t="n"/>
+      <c r="G38" s="57" t="n"/>
+      <c r="H38" s="57" t="n"/>
+      <c r="I38" s="57" t="n"/>
+      <c r="J38" s="58" t="n"/>
+      <c r="K38" s="79" t="inlineStr">
+        <is>
+          <t>round, round</t>
+        </is>
+      </c>
+      <c r="L38" s="57" t="n"/>
+      <c r="M38" s="57" t="n"/>
+      <c r="N38" s="58" t="n"/>
+      <c r="O38" s="82" t="inlineStr">
+        <is>
+          <t>Raw/derived only: a25_olda10, a25_olda11, a25_olda6, a25_olda8a9</t>
+        </is>
+      </c>
+      <c r="P38" s="57" t="n"/>
+      <c r="Q38" s="57" t="n"/>
+      <c r="R38" s="58" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="33">
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="B38:J38"/>
     <mergeCell ref="K37:N37"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="O37:R37"/>
